--- a/data/TY_Product_Database.xlsx
+++ b/data/TY_Product_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanfoo/Documents/Codex/2026-09-07/in/outputs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9099B2-E403-2D45-BF42-47DF2F9E9787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49048954-40D0-934A-987C-1752C0BEB375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33600" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33620" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3414" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1974">
   <si>
     <t>TY Product Database</t>
   </si>
@@ -5790,22 +5790,432 @@
     <t>Supports boiling with an optional pressure-cooking configuration.</t>
   </si>
   <si>
-    <t>Add each SKU under the matching brand section. Product must exactly match the Product Guide title. Keep Brand and SKU filled in.</t>
+    <t>Add each SKU in a yellow SKU cell under the matching Product, Type and Brand. Product and Type drive the Product Guide lineup and category tabs. Insert or copy another prepared row inside the same section when more space is needed.</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Brand section</t>
+  </si>
+  <si>
+    <t>Use yellow SKU cells</t>
+  </si>
+  <si>
+    <t>Chiller</t>
+  </si>
+  <si>
+    <t>Add SKU below</t>
+  </si>
+  <si>
+    <t>Enter SKU here</t>
+  </si>
+  <si>
+    <t>Freezer</t>
+  </si>
+  <si>
+    <t>Combination</t>
+  </si>
+  <si>
+    <t>Ice maker</t>
+  </si>
+  <si>
+    <t>Microwave oven</t>
+  </si>
+  <si>
+    <t>Speed oven</t>
+  </si>
+  <si>
+    <t>Blast freezer</t>
+  </si>
+  <si>
+    <t>YODA</t>
+  </si>
+  <si>
+    <t>Sliding glass</t>
+  </si>
+  <si>
+    <t>Swing top</t>
+  </si>
+  <si>
+    <t>Chilled</t>
+  </si>
+  <si>
+    <t>Ambient</t>
+  </si>
+  <si>
+    <t>Flower display</t>
+  </si>
+  <si>
+    <t>TY Innovations</t>
+  </si>
+  <si>
+    <t>Undercounter</t>
+  </si>
+  <si>
+    <t>Hood-type</t>
+  </si>
+  <si>
+    <t>Gravity</t>
+  </si>
+  <si>
+    <t>Pump</t>
+  </si>
+  <si>
+    <t>Heat treatment</t>
+  </si>
+  <si>
+    <t>Plug-in</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>A Series</t>
+  </si>
+  <si>
+    <t>B Series</t>
+  </si>
+  <si>
+    <t>Nuovair</t>
+  </si>
+  <si>
+    <t>Compact</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Electrolux</t>
+  </si>
+  <si>
+    <t>Granule</t>
+  </si>
+  <si>
+    <t>IFI</t>
+  </si>
+  <si>
+    <t>SAM 80</t>
+  </si>
+  <si>
+    <t>Esedra</t>
+  </si>
+  <si>
+    <t>Framec</t>
+  </si>
+  <si>
+    <t>Gelato display</t>
+  </si>
+  <si>
+    <t>Millennium</t>
+  </si>
+  <si>
+    <t>Bermuda View</t>
+  </si>
+  <si>
+    <t>Valmar</t>
+  </si>
+  <si>
+    <t>TTI Series</t>
+  </si>
+  <si>
+    <t>Quick Series</t>
+  </si>
+  <si>
+    <t>Mechanical Series</t>
+  </si>
+  <si>
+    <t>Gelmatic</t>
+  </si>
+  <si>
+    <t>Rational</t>
+  </si>
+  <si>
+    <t>Convection oven</t>
+  </si>
+  <si>
+    <t>iCombi Pro</t>
+  </si>
+  <si>
+    <t>iCombi Classic</t>
+  </si>
+  <si>
+    <t>iVario Pro</t>
   </si>
   <si>
     <t>UNOX</t>
   </si>
   <si>
+    <t>TOUCH</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
     <t>Merrychef</t>
   </si>
   <si>
+    <t>ConneX 12E</t>
+  </si>
+  <si>
+    <t>ConneX 12 SP</t>
+  </si>
+  <si>
+    <t>ConneX 16</t>
+  </si>
+  <si>
     <t>Eloma</t>
   </si>
   <si>
+    <t>Joker MT</t>
+  </si>
+  <si>
+    <t>Joker ST</t>
+  </si>
+  <si>
     <t>Firex</t>
   </si>
   <si>
-    <t>Other Brands</t>
+    <t>Multifunction cooker</t>
+  </si>
+  <si>
+    <t>Open Showcase Chiller (Inverter)</t>
+  </si>
+  <si>
+    <t>1000(W) x 770(D) x 1990(H)</t>
+  </si>
+  <si>
+    <t>505L (5 Shelves)</t>
+  </si>
+  <si>
+    <t>+1°C ~ +5°C</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz 
+13.8kW·h/24h / 15A Plug</t>
+  </si>
+  <si>
+    <t>1310(W) x 770(D) x 1990(H)</t>
+  </si>
+  <si>
+    <t>645L (5 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz
+14.2kW·h/24h / 15A Plug</t>
+  </si>
+  <si>
+    <t>1935(W) x 770(D) x 1990(H)</t>
+  </si>
+  <si>
+    <t>970L (5 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz
+26.5kW·h/24h / 15A Plug</t>
+  </si>
+  <si>
+    <t>RTCK-OPE-900C</t>
+  </si>
+  <si>
+    <t>RTCK-OPE-1200C</t>
+  </si>
+  <si>
+    <t>RTCK-OPE-1500C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> YDOP-SH750-15H-INV-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> YDOP-SH750-15H-INV-W</t>
+  </si>
+  <si>
+    <t>YDOP-SH750-15H-INV-B</t>
+  </si>
+  <si>
+    <t>YDOP-SH750-15H-INV-W</t>
+  </si>
+  <si>
+    <t>Ty Innovations</t>
+  </si>
+  <si>
+    <t>+2°C ~ +6°C</t>
+  </si>
+  <si>
+    <t>700(W) × 550(D) x 1500(H)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 
+50Hz / UK 13A Plug</t>
+  </si>
+  <si>
+    <t>900(W) × 700(D) × 1900(H)</t>
+  </si>
+  <si>
+    <t>1200(W) × 700(D) × 1900(H)</t>
+  </si>
+  <si>
+    <t>1500(W) × 700(D) x 1900(H)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz / 1.98kw / 10.6A / 15A Plug</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz / 2.20kw / 11.8A / 15A Plug</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz / 3.30kw / 17.7A / 15A Plug</t>
+  </si>
+  <si>
+    <t>1250(W) x 750(D) x 2000(H)</t>
+  </si>
+  <si>
+    <t>1079L (12 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50hz / 7.4kWh/24h /
+UK 13A Plug</t>
+  </si>
+  <si>
+    <t>RTGD-2DC-INV-B</t>
+  </si>
+  <si>
+    <t>1875W) x 750(D) x 2000(H)</t>
+  </si>
+  <si>
+    <t>1655L (18 Shelves)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1°C ~ +10°C </t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50hz / 12.5kW·h/24h /
+UK 13A Plug</t>
+  </si>
+  <si>
+    <t>RTGD-3DC-INV-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-2DSC-INV-W </t>
+  </si>
+  <si>
+    <t>Ext: 1170(W) x 633(D) x 1995(H)
+Int: 1074(W) x 500(D) x 1525(H)</t>
+  </si>
+  <si>
+    <t>720L
+(10 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50hz / 4.45kWh/24h / 
+UK 13A Plug</t>
+  </si>
+  <si>
+    <t>RTGD-2DSC-INV-B</t>
+  </si>
+  <si>
+    <t>Glass Display Chiller (Inverter)</t>
+  </si>
+  <si>
+    <t>Ext: 1770(W) x 633(D) x 1995(H)
+Int: 1674(W) x 500(D) x 1525(H)</t>
+  </si>
+  <si>
+    <t>1120L
+(15 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50hz / UK 13A Plug</t>
+  </si>
+  <si>
+    <t>RTGD-3DSC-INV-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-1DC-260-INV-W </t>
+  </si>
+  <si>
+    <t>Ext: 570(W) x 598(D) x 1560(H)
+Int: 484(W) x 470(D) x 1180(H)</t>
+  </si>
+  <si>
+    <t>264L
+(4 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V /
+1.06kWh/24h
+50Hz / UK 13A Plug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-1DC-260-INV-B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-1DC-330-INV-W </t>
+  </si>
+  <si>
+    <t>Ext: 668(W) x 656(D) x 1880(H)
+Int: 563(W) x 520(D) x 1603(H)</t>
+  </si>
+  <si>
+    <t>434L
+(5 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 
+1.32kWh/24h
+50Hz / UK 13A Plug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-1DC-330-INV-B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-1DC-208-INV-W </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTGD-1DC-208-INV-B </t>
+  </si>
+  <si>
+    <t>Ext: 406(W) x 579(D) x 1937(H)
+Int: 310(W) x 420(D) x 1492(H)</t>
+  </si>
+  <si>
+    <t>163L
+(6 Shelves)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0°C ~ +10°C </t>
+  </si>
+  <si>
+    <t>R600a</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V /
+1.1kWh/24h
+50Hz / UK 13A Plug</t>
+  </si>
+  <si>
+    <t>YDGD-1DC-400-B</t>
+  </si>
+  <si>
+    <t>+0 ̊C ~ +10 ̊C</t>
+  </si>
+  <si>
+    <t>With Lightbox
+630(W) x 630(D) x 2043(H)
+Light Box Dimensions: 
+530(W) x 197(H) mm</t>
+  </si>
+  <si>
+    <t>364L
+(5 Shelves)</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz /
+2.06kWh/24h /
+UK 13A Plug</t>
   </si>
 </sst>
 </file>
@@ -5819,7 +6229,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5888,8 +6298,62 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF294A5A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0A5A82"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF174A62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF4E7588"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF63808E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF8A6B1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5923,21 +6387,41 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDCEEF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF0A5A82"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDCEEF6"/>
+        <fgColor rgb="FFCFE8F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E7"/>
+        <fgColor rgb="FFEAF4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0BF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -6061,11 +6545,59 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8D6E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE5EDF1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7C56C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7C56C"/>
+      </right>
       <top style="thin">
-        <color rgb="FFE4EBEF"/>
+        <color rgb="FFE7C56C"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE4EBEF"/>
+        <color rgb="FFE7C56C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6073,47 +6605,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFE4EBEF"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD3E0E7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB9D7E5"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFB9D7E5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB9D7E5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFB9D7E5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB9D7E5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB9D7E5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB9D7E5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB9D7E5"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6127,7 +6622,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6251,49 +6746,37 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1"/>
@@ -6303,6 +6786,47 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -6313,7 +6837,11 @@
     <cellStyle name="Normal 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Percent" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6395,35 +6923,81 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ExStockTable" displayName="ExStockTable" ref="A1:I525" totalsRowShown="0">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Series"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Physical Qty"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Available Qty"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Clearance Price"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Retail Price"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Image"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Source Page"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InstructionsFilter" displayName="InstructionsFilter" ref="A6:C12" totalsRowShown="0">
+  <autoFilter ref="A6:C12" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Step"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Where"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="What to do"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ProductGuideTable" displayName="ProductGuideTable" ref="A1:H24" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ExStockTable" displayName="ExStockTable" ref="A1:I525" totalsRowShown="0">
+  <autoFilter ref="A1:I525" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="SKU"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Series"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Physical Qty"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Available Qty"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Clearance Price"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Retail Price"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Image"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Source Page"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="SpecificationsFilter" displayName="SpecificationsFilter" ref="A1:J104" totalsRowShown="0">
+  <autoFilter ref="A1:J104" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Brand"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SKU"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Product Name"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Dimension"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Capacity"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Temperature" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Refrigerant"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Energy Rating"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="EEG Claimable"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Power"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ProductGuideTable" displayName="ProductGuideTable" ref="A1:H24" totalsRowShown="0">
+  <autoFilter ref="A1:H24" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Product"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Brands &amp; Series"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Lead Time"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Our Focus"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Images"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Questions to Ask"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Important Notes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Category"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Product"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Brands &amp; Series"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Lead Time"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Our Focus"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Images"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Questions to Ask"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Important Notes"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="BrandLineupFilter" displayName="BrandLineupFilter" ref="A1:D417" totalsRowShown="0">
+  <autoFilter ref="A1:D417" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Product"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Brand"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="SKU"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -6612,28 +7186,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="A2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
@@ -6679,7 +7253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -6713,16 +7287,16 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6731,6 +7305,9 @@
     <mergeCell ref="A14:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -21062,7 +21639,7 @@
   <sheetPr>
     <tabColor rgb="FF0A5A82"/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -21070,7 +21647,7 @@
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="6" max="6" width="20" style="63" customWidth="1"/>
     <col min="7" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="44" customWidth="1"/>
   </cols>
@@ -21091,7 +21668,7 @@
       <c r="E1" s="31" t="s">
         <v>1476</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="61" t="s">
         <v>1477</v>
       </c>
       <c r="G1" s="31" t="s">
@@ -21115,7 +21692,7 @@
       <c r="C2" s="34"/>
       <c r="D2" s="34"/>
       <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="34"/>
       <c r="H2" s="34"/>
       <c r="I2" s="34"/>
@@ -21137,7 +21714,7 @@
       <c r="E3" s="37" t="s">
         <v>1484</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G3" s="37" t="s">
@@ -21169,7 +21746,7 @@
       <c r="E4" s="37" t="s">
         <v>1491</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G4" s="37" t="s">
@@ -21201,7 +21778,7 @@
       <c r="E5" s="37" t="s">
         <v>1494</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G5" s="37" t="s">
@@ -21233,7 +21810,7 @@
       <c r="E6" s="37" t="s">
         <v>1497</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G6" s="37" t="s">
@@ -21265,7 +21842,7 @@
       <c r="E7" s="37" t="s">
         <v>1484</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G7" s="37" t="s">
@@ -21297,7 +21874,7 @@
       <c r="E8" s="37" t="s">
         <v>1491</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G8" s="37" t="s">
@@ -21329,7 +21906,7 @@
       <c r="E9" s="37" t="s">
         <v>1504</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G9" s="37" t="s">
@@ -21361,7 +21938,7 @@
       <c r="E10" s="37" t="s">
         <v>1494</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G10" s="37" t="s">
@@ -21393,7 +21970,7 @@
       <c r="E11" s="37" t="s">
         <v>1509</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="36" t="s">
         <v>1510</v>
       </c>
       <c r="G11" s="37" t="s">
@@ -21425,7 +22002,7 @@
       <c r="E12" s="37" t="s">
         <v>1513</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="36" t="s">
         <v>1510</v>
       </c>
       <c r="G12" s="37" t="s">
@@ -21457,7 +22034,7 @@
       <c r="E13" s="37" t="s">
         <v>1516</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G13" s="37" t="s">
@@ -21489,7 +22066,7 @@
       <c r="E14" s="37" t="s">
         <v>1520</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G14" s="37" t="s">
@@ -21521,7 +22098,7 @@
       <c r="E15" s="37" t="s">
         <v>1523</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G15" s="37" t="s">
@@ -21553,7 +22130,7 @@
       <c r="E16" s="37" t="s">
         <v>1526</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G16" s="37" t="s">
@@ -21585,7 +22162,7 @@
       <c r="E17" s="37" t="s">
         <v>1529</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G17" s="37" t="s">
@@ -21617,7 +22194,7 @@
       <c r="E18" s="37" t="s">
         <v>1532</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G18" s="37" t="s">
@@ -21649,7 +22226,7 @@
       <c r="E19" s="37" t="s">
         <v>1535</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G19" s="37" t="s">
@@ -21681,7 +22258,7 @@
       <c r="E20" s="37" t="s">
         <v>1538</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G20" s="37" t="s">
@@ -21713,7 +22290,7 @@
       <c r="E21" s="37" t="s">
         <v>1516</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G21" s="37" t="s">
@@ -21745,7 +22322,7 @@
       <c r="E22" s="37" t="s">
         <v>1520</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G22" s="37" t="s">
@@ -21777,7 +22354,7 @@
       <c r="E23" s="37" t="s">
         <v>1523</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F23" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G23" s="37" t="s">
@@ -21809,7 +22386,7 @@
       <c r="E24" s="37" t="s">
         <v>1526</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G24" s="37" t="s">
@@ -21841,7 +22418,7 @@
       <c r="E25" s="37" t="s">
         <v>1529</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G25" s="37" t="s">
@@ -21873,7 +22450,7 @@
       <c r="E26" s="37" t="s">
         <v>1532</v>
       </c>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="36" t="s">
         <v>1499</v>
       </c>
       <c r="G26" s="37" t="s">
@@ -21905,7 +22482,7 @@
       <c r="E27" s="37" t="s">
         <v>1546</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="36" t="s">
         <v>1485</v>
       </c>
       <c r="G27" s="37" t="s">
@@ -21927,7 +22504,7 @@
       <c r="C28" s="30"/>
       <c r="D28" s="30"/>
       <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
+      <c r="F28" s="29"/>
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
       <c r="I28" s="30"/>
@@ -21941,7 +22518,7 @@
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
       <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
@@ -21963,7 +22540,7 @@
       <c r="E30" s="38" t="s">
         <v>1553</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G30" s="27" t="s">
@@ -21995,7 +22572,7 @@
       <c r="E31" s="27" t="s">
         <v>1559</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G31" s="27" t="s">
@@ -22027,7 +22604,7 @@
       <c r="E32" s="38" t="s">
         <v>1563</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G32" s="27" t="s">
@@ -22059,7 +22636,7 @@
       <c r="E33" s="27" t="s">
         <v>1566</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G33" s="27" t="s">
@@ -22091,7 +22668,7 @@
       <c r="E34" s="38" t="s">
         <v>1570</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G34" s="27" t="s">
@@ -22123,7 +22700,7 @@
       <c r="E35" s="38" t="s">
         <v>1574</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G35" s="27" t="s">
@@ -22155,7 +22732,7 @@
       <c r="E36" s="38" t="s">
         <v>1577</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G36" s="38" t="s">
@@ -22187,7 +22764,7 @@
       <c r="E37" s="27" t="s">
         <v>1580</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G37" s="27" t="s">
@@ -22219,7 +22796,7 @@
       <c r="E38" s="38" t="s">
         <v>1583</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G38" s="38" t="s">
@@ -22251,7 +22828,7 @@
       <c r="E39" s="38" t="s">
         <v>1589</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="39" t="s">
         <v>1554</v>
       </c>
       <c r="G39" s="38" t="s">
@@ -22283,7 +22860,7 @@
       <c r="E40" s="38" t="s">
         <v>1592</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="F40" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G40" s="27" t="s">
@@ -22315,7 +22892,7 @@
       <c r="E41" s="27" t="s">
         <v>1559</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="F41" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G41" s="27" t="s">
@@ -22347,7 +22924,7 @@
       <c r="E42" s="38" t="s">
         <v>1563</v>
       </c>
-      <c r="F42" s="27" t="s">
+      <c r="F42" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G42" s="27" t="s">
@@ -22379,7 +22956,7 @@
       <c r="E43" s="27" t="s">
         <v>1566</v>
       </c>
-      <c r="F43" s="27" t="s">
+      <c r="F43" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G43" s="27" t="s">
@@ -22411,7 +22988,7 @@
       <c r="E44" s="38" t="s">
         <v>1570</v>
       </c>
-      <c r="F44" s="27" t="s">
+      <c r="F44" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G44" s="27" t="s">
@@ -22443,7 +23020,7 @@
       <c r="E45" s="38" t="s">
         <v>1574</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G45" s="27" t="s">
@@ -22475,7 +23052,7 @@
       <c r="E46" s="38" t="s">
         <v>1602</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G46" s="27" t="s">
@@ -22507,7 +23084,7 @@
       <c r="E47" s="38" t="s">
         <v>1604</v>
       </c>
-      <c r="F47" s="27" t="s">
+      <c r="F47" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G47" s="27" t="s">
@@ -22539,7 +23116,7 @@
       <c r="E48" s="38" t="s">
         <v>1605</v>
       </c>
-      <c r="F48" s="27" t="s">
+      <c r="F48" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G48" s="27" t="s">
@@ -22571,7 +23148,7 @@
       <c r="E49" s="38" t="s">
         <v>1609</v>
       </c>
-      <c r="F49" s="27" t="s">
+      <c r="F49" s="39" t="s">
         <v>1593</v>
       </c>
       <c r="G49" s="27" t="s">
@@ -22795,7 +23372,7 @@
       <c r="E56" s="40" t="s">
         <v>1639</v>
       </c>
-      <c r="F56" s="41" t="s">
+      <c r="F56" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G56" s="38" t="s">
@@ -22825,7 +23402,7 @@
       <c r="E57" s="40" t="s">
         <v>1639</v>
       </c>
-      <c r="F57" s="41" t="s">
+      <c r="F57" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G57" s="38" t="s">
@@ -22855,7 +23432,7 @@
       <c r="E58" s="40" t="s">
         <v>1644</v>
       </c>
-      <c r="F58" s="41" t="s">
+      <c r="F58" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G58" s="38" t="s">
@@ -22885,7 +23462,7 @@
       <c r="E59" s="40" t="s">
         <v>1644</v>
       </c>
-      <c r="F59" s="41" t="s">
+      <c r="F59" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G59" s="38" t="s">
@@ -22915,7 +23492,7 @@
       <c r="E60" s="38" t="s">
         <v>1647</v>
       </c>
-      <c r="F60" s="41" t="s">
+      <c r="F60" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G60" s="38" t="s">
@@ -22947,7 +23524,7 @@
       <c r="E61" s="38" t="s">
         <v>1647</v>
       </c>
-      <c r="F61" s="41" t="s">
+      <c r="F61" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G61" s="38" t="s">
@@ -22977,7 +23554,7 @@
       <c r="E62" s="38" t="s">
         <v>1652</v>
       </c>
-      <c r="F62" s="41" t="s">
+      <c r="F62" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G62" s="38" t="s">
@@ -23007,7 +23584,7 @@
       <c r="E63" s="38" t="s">
         <v>1652</v>
       </c>
-      <c r="F63" s="41" t="s">
+      <c r="F63" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G63" s="38" t="s">
@@ -23039,7 +23616,7 @@
       <c r="E64" s="38" t="s">
         <v>1655</v>
       </c>
-      <c r="F64" s="41" t="s">
+      <c r="F64" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G64" s="38" t="s">
@@ -23069,7 +23646,7 @@
       <c r="E65" s="38" t="s">
         <v>1655</v>
       </c>
-      <c r="F65" s="41" t="s">
+      <c r="F65" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G65" s="38" t="s">
@@ -23101,7 +23678,7 @@
       <c r="E66" s="38" t="s">
         <v>1659</v>
       </c>
-      <c r="F66" s="41" t="s">
+      <c r="F66" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G66" s="38" t="s">
@@ -23131,7 +23708,7 @@
       <c r="E67" s="38" t="s">
         <v>1659</v>
       </c>
-      <c r="F67" s="41" t="s">
+      <c r="F67" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G67" s="38" t="s">
@@ -23163,7 +23740,7 @@
       <c r="E68" s="38" t="s">
         <v>1662</v>
       </c>
-      <c r="F68" s="41" t="s">
+      <c r="F68" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G68" s="38" t="s">
@@ -23195,7 +23772,7 @@
       <c r="E69" s="38" t="s">
         <v>1662</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="F69" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G69" s="38" t="s">
@@ -23225,7 +23802,7 @@
       <c r="E70" s="38" t="s">
         <v>1666</v>
       </c>
-      <c r="F70" s="41" t="s">
+      <c r="F70" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G70" s="38" t="s">
@@ -23255,7 +23832,7 @@
       <c r="E71" s="38" t="s">
         <v>1666</v>
       </c>
-      <c r="F71" s="41" t="s">
+      <c r="F71" s="42" t="s">
         <v>1554</v>
       </c>
       <c r="G71" s="38" t="s">
@@ -24023,13 +24600,920 @@
       </c>
       <c r="J104" s="27"/>
     </row>
+    <row r="106" spans="1:10" ht="16" x14ac:dyDescent="0.15">
+      <c r="A106" s="57" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B106" s="58"/>
+      <c r="C106" s="59"/>
+      <c r="D106" s="59"/>
+      <c r="E106" s="59"/>
+      <c r="F106" s="58"/>
+      <c r="G106" s="59"/>
+      <c r="H106" s="59"/>
+      <c r="I106" s="59"/>
+      <c r="J106" s="59"/>
+    </row>
+    <row r="107" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A107" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B107" s="60" t="s">
+        <v>690</v>
+      </c>
+      <c r="C107" s="60" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D107" s="60" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E107" s="60" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F107" s="62" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G107" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H107" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I107" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J107" s="60" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A108" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B108" s="60" t="s">
+        <v>694</v>
+      </c>
+      <c r="C108" s="60" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D108" s="60" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E108" s="60" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F108" s="62" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G108" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H108" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I108" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J108" s="60" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A109" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B109" s="60" t="s">
+        <v>697</v>
+      </c>
+      <c r="C109" s="60" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D109" s="41" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E109" s="60" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F109" s="62" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G109" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H109" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I109" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J109" s="60" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A110" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B110" s="60" t="s">
+        <v>700</v>
+      </c>
+      <c r="C110" s="60" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D110" s="41" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E110" s="60" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F110" s="62" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G110" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H110" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I110" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J110" s="60" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A111" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>703</v>
+      </c>
+      <c r="C111" s="60" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D111" s="60" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E111" s="60" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F111" s="62" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G111" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H111" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I111" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J111" s="60" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A112" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B112" s="60" t="s">
+        <v>706</v>
+      </c>
+      <c r="C112" s="60" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D112" s="60" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E112" s="60" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F112" s="62" t="s">
+        <v>1908</v>
+      </c>
+      <c r="G112" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H112" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I112" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J112" s="60" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="14" x14ac:dyDescent="0.15">
+      <c r="A113" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B113" s="60" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C113" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D113" s="60" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E113" s="60" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F113" s="62" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G113" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H113" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I113" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J113" s="60" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="14" x14ac:dyDescent="0.15">
+      <c r="A114" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C114" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D114" s="60" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E114" s="60" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F114" s="62" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G114" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H114" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I114" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J114" s="60" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="14" x14ac:dyDescent="0.15">
+      <c r="A115" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B115" s="60" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C115" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D115" s="60" t="s">
+        <v>1929</v>
+      </c>
+      <c r="E115" s="60" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F115" s="62" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G115" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H115" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I115" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J115" s="60" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A116" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B116" s="60" t="s">
+        <v>508</v>
+      </c>
+      <c r="C116" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D116" s="60" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E116" s="67" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F116" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G116" s="69" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H116" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I116" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J116" s="60" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A117" s="60" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B117" s="60" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C117" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D117" s="60" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E117" s="67" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F117" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G117" s="69" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H117" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I117" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J117" s="60" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A118" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B118" s="66" t="s">
+        <v>510</v>
+      </c>
+      <c r="C118" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D118" s="66" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E118" s="68" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F118" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G118" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H118" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I118" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J118" s="66" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A119" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B119" s="66" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C119" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D119" s="66" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E119" s="68" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F119" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G119" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H119" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I119" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J119" s="66" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A120" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B120" s="66" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C120" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D120" s="66" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E120" s="68" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F120" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G120" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H120" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I120" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J120" s="66" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A121" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B121" s="66" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C121" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D121" s="66" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E121" s="68" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F121" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G121" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H121" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I121" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J121" s="66" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A122" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B122" s="66" t="s">
+        <v>515</v>
+      </c>
+      <c r="C122" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D122" s="66" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E122" s="68" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F122" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G122" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H122" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I122" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J122" s="66" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A123" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B123" s="66" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C123" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D123" s="66" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E123" s="68" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F123" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G123" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H123" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I123" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J123" s="66" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="42" x14ac:dyDescent="0.15">
+      <c r="A124" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B124" s="66" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C124" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D124" s="66" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E124" s="68" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F124" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G124" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H124" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I124" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J124" s="66" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="42" x14ac:dyDescent="0.15">
+      <c r="A125" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B125" s="66" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C125" s="60" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D125" s="66" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E125" s="68" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F125" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G125" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H125" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I125" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J125" s="66" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="42" x14ac:dyDescent="0.15">
+      <c r="A126" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B126" s="66" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C126" s="66" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D126" s="66" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E126" s="68" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F126" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G126" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H126" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I126" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J126" s="66" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="42" x14ac:dyDescent="0.15">
+      <c r="A127" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B127" s="66" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C127" s="66" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D127" s="66" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E127" s="68" t="s">
+        <v>1959</v>
+      </c>
+      <c r="F127" s="41" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G127" s="66" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H127" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I127" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J127" s="66" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="42" x14ac:dyDescent="0.15">
+      <c r="A128" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B128" s="66" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C128" s="66" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D128" s="66" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E128" s="68" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F128" s="41" t="s">
+        <v>1966</v>
+      </c>
+      <c r="G128" s="66" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H128" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I128" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J128" s="66" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="42" x14ac:dyDescent="0.15">
+      <c r="A129" s="65" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B129" s="66" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C129" s="66" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D129" s="66" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E129" s="68" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F129" s="41" t="s">
+        <v>1966</v>
+      </c>
+      <c r="G129" s="66" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H129" s="66" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I129" s="66" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J129" s="66" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A130" s="70"/>
+      <c r="B130" s="70"/>
+      <c r="C130" s="64"/>
+      <c r="D130" s="70"/>
+      <c r="E130" s="70"/>
+      <c r="F130" s="71"/>
+      <c r="G130" s="70"/>
+      <c r="H130" s="70"/>
+      <c r="I130" s="70"/>
+      <c r="J130" s="70"/>
+    </row>
+    <row r="133" spans="1:10" ht="16" x14ac:dyDescent="0.15">
+      <c r="A133" s="57" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B133" s="58"/>
+      <c r="C133" s="59"/>
+      <c r="D133" s="59"/>
+      <c r="E133" s="59"/>
+      <c r="F133" s="58"/>
+      <c r="G133" s="59"/>
+      <c r="H133" s="59"/>
+      <c r="I133" s="59"/>
+      <c r="J133" s="59"/>
+    </row>
+    <row r="134" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A134" s="60" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B134" s="60" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C134" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D134" s="60" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E134" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F134" s="62" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G134" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H134" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I134" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J134" s="60" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="28" x14ac:dyDescent="0.15">
+      <c r="A135" s="60" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B135" s="60" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C135" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D135" s="60" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E135" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F135" s="62" t="s">
+        <v>1924</v>
+      </c>
+      <c r="G135" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H135" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I135" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J135" s="60" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="56" x14ac:dyDescent="0.15">
+      <c r="A136" s="60" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B136" s="60" t="s">
+        <v>636</v>
+      </c>
+      <c r="C136" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D136" s="60" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E136" s="60" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F136" s="41" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G136" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H136" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I136" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J136" s="60" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="56" x14ac:dyDescent="0.15">
+      <c r="A137" s="60" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B137" s="60" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C137" s="60" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D137" s="60" t="s">
+        <v>1971</v>
+      </c>
+      <c r="E137" s="60" t="s">
+        <v>1972</v>
+      </c>
+      <c r="F137" s="41" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G137" s="60" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H137" s="60" t="s">
+        <v>1556</v>
+      </c>
+      <c r="I137" s="60" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J137" s="60" t="s">
+        <v>1973</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="L31:L104 I30:I104" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="L31:L104 I30:I104 I134:I137 I107:I117" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Yes,No,Pending,Not applicable"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -24681,1026 +26165,5859 @@
   <sheetPr>
     <tabColor rgb="FF0A5A82"/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:D420"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="43" t="s">
         <v>1686</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>1473</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="D1" s="45" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="47" t="s">
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="46" t="s">
         <v>1482</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="54"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="46" t="s">
+      <c r="B2" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C3" s="48" t="s">
         <v>1482</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="D3" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="46" t="s">
+    <row r="5" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B5" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C5" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="D5" s="50" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="46" t="s">
+    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B6" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C6" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="D6" s="50" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="46" t="s">
+    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B7" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C7" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="D7" s="50" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="46" t="s">
+    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B8" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C8" s="52" t="s">
         <v>1482</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="D8" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="48" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D11" s="50" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="46" t="s">
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B12" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C12" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="D12" s="50" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="46" t="s">
+    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B13" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C13" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="D13" s="50" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="46" t="s">
+    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B14" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C14" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="D14" s="50" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="46" t="s">
+    <row r="15" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B15" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C15" s="52" t="s">
         <v>1482</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="D15" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="48" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D18" s="50" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="46" t="s">
+    <row r="19" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="50" t="s">
         <v>1694</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B19" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C19" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="D19" s="50" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="46" t="s">
+    <row r="20" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="48" t="s">
         <v>1701</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B22" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C22" s="48" t="s">
         <v>1482</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="D22" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D32" s="50" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="46" t="s">
+    <row r="33" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B33" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C33" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="D33" s="50" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="46" t="s">
+    <row r="34" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B34" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C34" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="D34" s="50" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="46" t="s">
+    <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B35" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C35" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="D35" s="50" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="46" t="s">
+    <row r="36" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B36" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C36" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="D36" s="50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="46" t="s">
+    <row r="37" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B37" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C37" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="D37" s="50" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="46" t="s">
+    <row r="38" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B38" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C38" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="D38" s="50" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="46" t="s">
+    <row r="39" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="50" t="s">
         <v>1701</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B39" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C39" s="51" t="s">
         <v>1482</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="D39" s="50" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="46" t="s">
+    <row r="40" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B40" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C40" s="52" t="s">
         <v>1482</v>
       </c>
-      <c r="C21" s="55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="46" t="s">
+      <c r="D40" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B41" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C41" s="52" t="s">
         <v>1482</v>
       </c>
-      <c r="C22" s="55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="46" t="s">
+      <c r="D41" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="48" t="s">
         <v>1701</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B42" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C42" s="48" t="s">
         <v>1482</v>
       </c>
-      <c r="C23" s="55" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="46" t="s">
+      <c r="D42" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B43" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C43" s="52" t="s">
         <v>1482</v>
       </c>
-      <c r="C24" s="55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="46" t="s">
+      <c r="D43" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B44" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C44" s="52" t="s">
         <v>1482</v>
       </c>
-      <c r="C25" s="55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="46" t="s">
+      <c r="D44" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="48" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B45" s="48" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C45" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D45" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="52" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B46" s="52" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C46" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="52" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B47" s="52" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B48" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C48" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D48" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B49" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B50" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C50" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B51" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C51" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D51" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B52" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C52" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B53" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C53" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="48" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B54" s="48" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C54" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D54" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="52" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B55" s="52" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C55" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="52" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B56" s="52" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C56" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="48" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B57" s="48" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C57" s="48" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D57" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B58" s="52" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C58" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B59" s="52" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C59" s="52" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="46" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B60" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C60" s="47" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D60" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="48" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B61" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C61" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D61" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B62" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C62" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D62" s="50" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B63" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C63" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D63" s="50" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C64" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D64" s="50" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B65" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C65" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D65" s="50" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B66" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D66" s="50" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B67" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C67" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C68" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D68" s="50" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B69" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C69" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D69" s="50" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B70" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C70" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D70" s="50" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B71" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C71" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D71" s="50" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B72" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C72" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D72" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B73" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C73" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D73" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="48" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B74" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C74" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D74" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B75" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C75" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D75" s="50" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B76" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C76" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D76" s="50" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B77" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C77" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D77" s="50" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B78" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C78" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D78" s="50" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B79" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C79" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D79" s="50" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B80" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C80" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D80" s="50" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B81" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C81" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D81" s="50" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B82" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C82" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D82" s="50" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B83" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C83" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D83" s="50" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B84" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C84" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D84" s="50" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B85" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C85" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D85" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B86" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C86" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D86" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="48" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B87" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C87" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D87" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B88" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C88" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D88" s="50" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B89" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C89" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D89" s="50" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B90" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C90" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D90" s="50" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B91" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C91" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D91" s="50" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B92" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C92" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D92" s="50" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="50" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B93" s="50" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C93" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D93" s="50" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B94" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C94" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D94" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="52" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B95" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C95" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D95" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="48" t="s">
         <v>1701</v>
       </c>
-      <c r="B26" s="51" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="48"/>
-      <c r="B27" s="52" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C27" s="56"/>
-    </row>
-    <row r="28" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="48"/>
-      <c r="B28" s="52" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C28" s="56"/>
-    </row>
-    <row r="29" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="48"/>
-      <c r="B29" s="52" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C29" s="56"/>
-    </row>
-    <row r="30" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="47" t="s">
+      <c r="B96" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C96" s="48" t="s">
         <v>1550</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="54"/>
-    </row>
-    <row r="31" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="46" t="s">
+      <c r="D96" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B97" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C97" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D97" s="50" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B98" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C98" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D98" s="50" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B99" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C99" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D99" s="50" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B100" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C100" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D100" s="50" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B101" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C101" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D101" s="50" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B102" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C102" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D102" s="50" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B103" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C103" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D103" s="50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B104" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C104" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D104" s="50" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B105" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C105" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D105" s="50" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B106" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C106" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D106" s="50" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B107" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C107" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D107" s="50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B108" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C108" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D108" s="50" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B109" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C109" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D109" s="50" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B110" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C110" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D110" s="50" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B111" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C111" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D111" s="50" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B112" s="50" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C112" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D112" s="50" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B113" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C113" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D113" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B114" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C114" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D114" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B115" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C115" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D115" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A116" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B116" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C116" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D116" s="50" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A117" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B117" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C117" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D117" s="50" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B118" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C118" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D118" s="50" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B119" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C119" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D119" s="50" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B120" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C120" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D120" s="50" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B121" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C121" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D121" s="50" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B122" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C122" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D122" s="50" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B123" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C123" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D123" s="50" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B124" s="50" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C124" s="51" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D124" s="50" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A125" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B125" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C125" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D125" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B126" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D126" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B127" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C127" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D127" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A128" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B128" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C128" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D128" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A129" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B129" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C129" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D129" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="48" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B130" s="48" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C130" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D130" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B131" s="52" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C131" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D131" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B132" s="52" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C132" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D132" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="48" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B133" s="48" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C133" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D133" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="52" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B134" s="52" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C134" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D134" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="52" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B135" s="52" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C135" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D135" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B136" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C136" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D136" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A137" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B137" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C137" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D137" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A138" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B138" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C138" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D138" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A139" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B139" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C139" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D139" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A140" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B140" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C140" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D140" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A141" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B141" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C141" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D141" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="48" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B142" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C142" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D142" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A143" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B143" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C143" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D143" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A144" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B144" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C144" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D144" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="48" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B145" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C145" s="48" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D145" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B146" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C146" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D146" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A147" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B147" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C147" s="52" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D147" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="46" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B148" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C148" s="47" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D148" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B31" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="46" t="s">
+      <c r="B149" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C149" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D149" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A150" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B32" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="46" t="s">
+      <c r="B150" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C150" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D150" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A151" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B33" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>1561</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="46" t="s">
+      <c r="B151" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C151" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D151" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A152" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B34" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="46" t="s">
+      <c r="B152" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C152" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D152" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A153" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B35" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>1567</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="46" t="s">
+      <c r="B153" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C153" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D153" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A154" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B36" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>1572</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46" t="s">
+      <c r="B154" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C154" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D154" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A155" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B37" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="46" t="s">
+      <c r="B155" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C155" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D155" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A156" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B38" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="46" t="s">
+      <c r="B156" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C156" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D156" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A157" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B39" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>1581</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="46" t="s">
+      <c r="B157" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C157" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D157" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A158" s="48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B158" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C158" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D158" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A159" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B159" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C159" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D159" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A160" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B160" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C160" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D160" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A161" s="48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B161" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C161" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D161" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A162" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B162" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C162" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D162" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A163" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B163" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C163" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D163" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A164" s="48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B164" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C164" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D164" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A165" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B165" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C165" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D165" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A166" s="52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B166" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C166" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D166" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A167" s="48" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B167" s="48" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C167" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D167" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A168" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B168" s="52" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C168" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D168" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B169" s="52" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C169" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D169" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A170" s="48" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B170" s="48" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C170" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D170" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A171" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B171" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C171" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D171" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A172" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B172" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C172" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D172" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A173" s="48" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B173" s="48" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C173" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D173" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A174" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B174" s="52" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C174" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D174" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A175" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B175" s="52" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C175" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D175" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A176" s="48" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B176" s="48" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C176" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D176" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A177" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B177" s="52" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C177" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D177" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A178" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B178" s="52" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C178" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D178" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A179" s="48" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B179" s="48" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C179" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D179" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A180" s="52" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B180" s="52" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C180" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D180" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A181" s="52" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B181" s="52" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C181" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D181" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A182" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B182" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C182" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D182" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B183" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C183" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D183" s="53" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A184" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B184" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C184" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D184" s="53" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A185" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B185" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C185" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D185" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A186" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B186" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C186" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D186" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A187" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B187" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C187" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D187" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A188" s="48" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B188" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C188" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D188" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A189" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B189" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C189" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D189" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A190" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B190" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C190" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D190" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A191" s="48" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B191" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C191" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D191" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A192" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B192" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C192" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D192" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A193" s="52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B193" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C193" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D193" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A194" s="48" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B194" s="48" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C194" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D194" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A195" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B195" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C195" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D195" s="53" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A196" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B196" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C196" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D196" s="53" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A197" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B197" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C197" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D197" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A198" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B198" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C198" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D198" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A199" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B199" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C199" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D199" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A200" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B200" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C200" s="48" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D200" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A201" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B201" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C201" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D201" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A202" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B202" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C202" s="52" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D202" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A203" s="46" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B203" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C203" s="47" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D203" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A204" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B40" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>1586</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="46" t="s">
+      <c r="B204" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C204" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D204" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A205" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B41" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="46" t="s">
+      <c r="B205" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C205" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D205" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A206" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B42" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C42" s="27" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="46" t="s">
+      <c r="B206" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C206" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D206" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A207" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B43" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="46" t="s">
+      <c r="B207" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C207" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D207" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A208" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B44" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C44" s="27" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="46" t="s">
+      <c r="B208" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C208" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D208" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A209" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B45" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>1597</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="46" t="s">
+      <c r="B209" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C209" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D209" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A210" s="48" t="s">
         <v>1694</v>
       </c>
-      <c r="B46" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="46" t="s">
+      <c r="B210" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C210" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D210" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A211" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B47" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="46" t="s">
+      <c r="B211" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C211" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D211" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A212" s="52" t="s">
         <v>1694</v>
       </c>
-      <c r="B48" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B49" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B50" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B51" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C51" s="38" t="s">
-        <v>1611</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B52" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B53" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C53" s="38" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B54" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B55" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>1627</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="46" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B56" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C56" s="38" t="s">
-        <v>1631</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="46" t="s">
+      <c r="B212" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C212" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D212" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A213" s="48" t="s">
         <v>1701</v>
       </c>
-      <c r="B57" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="46" t="s">
+      <c r="B213" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C213" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D213" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A214" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B58" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>1641</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="46" t="s">
+      <c r="B214" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C214" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D214" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A215" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B59" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>1642</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="46" t="s">
+      <c r="B215" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C215" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D215" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A216" s="48" t="s">
         <v>1701</v>
       </c>
-      <c r="B60" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C60" s="38" t="s">
-        <v>1645</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="46" t="s">
+      <c r="B216" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C216" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D216" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A217" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B61" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="46" t="s">
+      <c r="B217" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C217" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D217" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A218" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B62" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C62" s="38" t="s">
-        <v>1649</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="46" t="s">
+      <c r="B218" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C218" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D218" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A219" s="48" t="s">
         <v>1701</v>
       </c>
-      <c r="B63" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C63" s="27" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="46" t="s">
+      <c r="B219" s="48" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C219" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D219" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A220" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B64" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C64" s="38" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="46" t="s">
+      <c r="B220" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C220" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D220" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A221" s="52" t="s">
         <v>1701</v>
       </c>
-      <c r="B65" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C65" s="27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B66" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C66" s="38" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B67" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B68" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C68" s="38" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B69" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C69" s="27" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B70" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C70" s="38" t="s">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B71" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C71" s="27" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B72" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C72" s="38" t="s">
-        <v>1667</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B73" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C73" s="38" t="s">
-        <v>1668</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B74" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C74" s="38" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B75" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C75" s="38" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B76" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C76" s="38" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B77" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C77" s="38" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B78" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C78" s="27" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B79" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B80" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C80" s="38" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="46" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B81" s="52" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C81" s="38" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="47" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B82" s="50"/>
-      <c r="C82" s="54"/>
-    </row>
-    <row r="83" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="48"/>
-      <c r="B83" s="52" t="s">
-        <v>1842</v>
-      </c>
-      <c r="C83" s="56"/>
-    </row>
-    <row r="84" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="48"/>
-      <c r="B84" s="52" t="s">
-        <v>1842</v>
-      </c>
-      <c r="C84" s="56"/>
-    </row>
-    <row r="85" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="48"/>
-      <c r="B85" s="52" t="s">
-        <v>1842</v>
-      </c>
-      <c r="C85" s="56"/>
-    </row>
-    <row r="86" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="47" t="s">
+      <c r="B221" s="52" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C221" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D221" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A222" s="48" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B222" s="48" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C222" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D222" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A223" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B223" s="52" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C223" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D223" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A224" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B224" s="52" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C224" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D224" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A225" s="48" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B225" s="48" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C225" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D225" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A226" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B226" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C226" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D226" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A227" s="52" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B227" s="52" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C227" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D227" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A228" s="48" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B228" s="48" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C228" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D228" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A229" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B229" s="52" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C229" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D229" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A230" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B230" s="52" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C230" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D230" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A231" s="48" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B231" s="48" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C231" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D231" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A232" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B232" s="52" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C232" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D232" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A233" s="52" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B233" s="52" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C233" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D233" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A234" s="48" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B234" s="48" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C234" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D234" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A235" s="52" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B235" s="52" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C235" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D235" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A236" s="52" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B236" s="52" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C236" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D236" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A237" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B237" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C237" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D237" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A238" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B238" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C238" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D238" s="53" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A239" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B239" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C239" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D239" s="53" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A240" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B240" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C240" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D240" s="53" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A241" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B241" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C241" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D241" s="53" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A242" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B242" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C242" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D242" s="53" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A243" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B243" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C243" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D243" s="53" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A244" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B244" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C244" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D244" s="53" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A245" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B245" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C245" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D245" s="53" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A246" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B246" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C246" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D246" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A247" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B247" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C247" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D247" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A248" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B248" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C248" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D248" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A249" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B249" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C249" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D249" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A250" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B250" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C250" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D250" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A251" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B251" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C251" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D251" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A252" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B252" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C252" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D252" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A253" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B253" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C253" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D253" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A254" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B254" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C254" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D254" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A255" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B255" s="48" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C255" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D255" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A256" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B256" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C256" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D256" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A257" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B257" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C257" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D257" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A258" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B258" s="48" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C258" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D258" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A259" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B259" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C259" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D259" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A260" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B260" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C260" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D260" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A261" s="48" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B261" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C261" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D261" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A262" s="52" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B262" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C262" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D262" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A263" s="52" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B263" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C263" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D263" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A264" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B264" s="48" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C264" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D264" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A265" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B265" s="52" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C265" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D265" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A266" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B266" s="52" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C266" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D266" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A267" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B267" s="48" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C267" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D267" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A268" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B268" s="52" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C268" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D268" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A269" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B269" s="52" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C269" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D269" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A270" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B270" s="48" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C270" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D270" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A271" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B271" s="52" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C271" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D271" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A272" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B272" s="52" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C272" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D272" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A273" s="48" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B273" s="48" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C273" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D273" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A274" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B274" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C274" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D274" s="53" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A275" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B275" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C275" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D275" s="53" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A276" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B276" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C276" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D276" s="53" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A277" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B277" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C277" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D277" s="53" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A278" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B278" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C278" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D278" s="53" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A279" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B279" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C279" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D279" s="53" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A280" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B280" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C280" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D280" s="53" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A281" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B281" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C281" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D281" s="53" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A282" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B282" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C282" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D282" s="53" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A283" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B283" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C283" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D283" s="53" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A284" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B284" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C284" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D284" s="53" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A285" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B285" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C285" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D285" s="53" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A286" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B286" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C286" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D286" s="53" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A287" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B287" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C287" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D287" s="53" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A288" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B288" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C288" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D288" s="53" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A289" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B289" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C289" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D289" s="53" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A290" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B290" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C290" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D290" s="53" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A291" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B291" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C291" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D291" s="53" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A292" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B292" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C292" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D292" s="53" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A293" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B293" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C293" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D293" s="53" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A294" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B294" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C294" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D294" s="53" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A295" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B295" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C295" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D295" s="53" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A296" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B296" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C296" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D296" s="53" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A297" s="48" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B297" s="48" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C297" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D297" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A298" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B298" s="52" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C298" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D298" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A299" s="52" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B299" s="52" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C299" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D299" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A300" s="48" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B300" s="48" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C300" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D300" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A301" s="52" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B301" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C301" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D301" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A302" s="52" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B302" s="52" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C302" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D302" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A303" s="48" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B303" s="48" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C303" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D303" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A304" s="52" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B304" s="52" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C304" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D304" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A305" s="52" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B305" s="52" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C305" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D305" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A306" s="48" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B306" s="48" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C306" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D306" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A307" s="52" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B307" s="52" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C307" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D307" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A308" s="52" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B308" s="52" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C308" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D308" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A309" s="48" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B309" s="48" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C309" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D309" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A310" s="52" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B310" s="52" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C310" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D310" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A311" s="52" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B311" s="52" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C311" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D311" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A312" s="46" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B312" s="47" t="s">
         <v>1843</v>
       </c>
-      <c r="B86" s="50"/>
-      <c r="C86" s="54"/>
-    </row>
-    <row r="87" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="48"/>
-      <c r="B87" s="52" t="s">
+      <c r="C312" s="47" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D312" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A313" s="48" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B313" s="48" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C313" s="48" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D313" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A314" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B314" s="52" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C314" s="52" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D314" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A315" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B315" s="52" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C315" s="52" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D315" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A316" s="48" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B316" s="48" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C316" s="48" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D316" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A317" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B317" s="52" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C317" s="52" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D317" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A318" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B318" s="52" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C318" s="52" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D318" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A319" s="48" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B319" s="48" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C319" s="48" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D319" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A320" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B320" s="52" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C320" s="52" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D320" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A321" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B321" s="52" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C321" s="52" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D321" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A322" s="46" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B322" s="47" t="s">
         <v>1843</v>
       </c>
-      <c r="C87" s="56"/>
-    </row>
-    <row r="88" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="48"/>
-      <c r="B88" s="52" t="s">
+      <c r="C322" s="47" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D322" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A323" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B323" s="48" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C323" s="48" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D323" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A324" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B324" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C324" s="52" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D324" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A325" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B325" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C325" s="52" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D325" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A326" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B326" s="48" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C326" s="48" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D326" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A327" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B327" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C327" s="52" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D327" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A328" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B328" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C328" s="52" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D328" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A329" s="46" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B329" s="47" t="s">
         <v>1843</v>
       </c>
-      <c r="C88" s="56"/>
-    </row>
-    <row r="89" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="48"/>
-      <c r="B89" s="52" t="s">
+      <c r="C329" s="47" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D329" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A330" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B330" s="48" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C330" s="48" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D330" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A331" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B331" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C331" s="52" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D331" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A332" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B332" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C332" s="52" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D332" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A333" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B333" s="48" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C333" s="48" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D333" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A334" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B334" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C334" s="52" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D334" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A335" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B335" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C335" s="52" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D335" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A336" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B336" s="48" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C336" s="48" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D336" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A337" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B337" s="52" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C337" s="52" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D337" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A338" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B338" s="52" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C338" s="52" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D338" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A339" s="46" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B339" s="47" t="s">
         <v>1843</v>
       </c>
-      <c r="C89" s="56"/>
-    </row>
-    <row r="90" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="47" t="s">
+      <c r="C339" s="47" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D339" s="47" t="s">
         <v>1844</v>
       </c>
-      <c r="B90" s="50"/>
-      <c r="C90" s="54"/>
-    </row>
-    <row r="91" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="48"/>
-      <c r="B91" s="52" t="s">
+    </row>
+    <row r="340" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A340" s="48" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B340" s="48" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C340" s="48" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D340" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A341" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B341" s="52" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C341" s="52" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D341" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A342" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B342" s="52" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C342" s="52" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D342" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A343" s="48" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B343" s="48" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C343" s="48" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D343" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A344" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B344" s="52" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C344" s="52" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D344" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A345" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B345" s="52" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C345" s="52" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D345" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A346" s="46" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B346" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C346" s="47" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D346" s="47" t="s">
         <v>1844</v>
       </c>
-      <c r="C91" s="56"/>
-    </row>
-    <row r="92" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="48"/>
-      <c r="B92" s="52" t="s">
+    </row>
+    <row r="347" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A347" s="48" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B347" s="48" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C347" s="48" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D347" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A348" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B348" s="52" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C348" s="52" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D348" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A349" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B349" s="52" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C349" s="52" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D349" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A350" s="46" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B350" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C350" s="47" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D350" s="47" t="s">
         <v>1844</v>
       </c>
-      <c r="C92" s="56"/>
-    </row>
-    <row r="93" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="48"/>
-      <c r="B93" s="52" t="s">
+    </row>
+    <row r="351" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A351" s="48" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B351" s="48" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C351" s="48" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D351" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A352" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B352" s="52" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C352" s="52" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D352" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A353" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B353" s="52" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C353" s="52" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D353" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A354" s="48" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B354" s="48" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C354" s="48" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D354" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A355" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B355" s="52" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C355" s="52" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D355" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A356" s="52" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B356" s="52" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C356" s="52" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D356" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A357" s="46" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B357" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C357" s="47" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D357" s="47" t="s">
         <v>1844</v>
       </c>
-      <c r="C93" s="56"/>
-    </row>
-    <row r="94" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="47" t="s">
-        <v>1845</v>
-      </c>
-      <c r="B94" s="50"/>
-      <c r="C94" s="54"/>
-    </row>
-    <row r="95" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="48"/>
-      <c r="B95" s="52" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C95" s="56"/>
-    </row>
-    <row r="96" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="48"/>
-      <c r="B96" s="52" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C96" s="56"/>
-    </row>
-    <row r="97" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="48"/>
-      <c r="B97" s="52" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C97" s="56"/>
-    </row>
-    <row r="98" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="47" t="s">
+    </row>
+    <row r="358" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A358" s="48" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B358" s="48" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C358" s="48" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D358" s="49" t="s">
         <v>1846</v>
       </c>
-      <c r="B98" s="50"/>
-      <c r="C98" s="54"/>
-    </row>
-    <row r="99" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="48"/>
-      <c r="B99" s="52" t="s">
+    </row>
+    <row r="359" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A359" s="52" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B359" s="52" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C359" s="52" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D359" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A360" s="52" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B360" s="52" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C360" s="52" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D360" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A361" s="48" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B361" s="48" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C361" s="48" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D361" s="49" t="s">
         <v>1846</v>
       </c>
-      <c r="C99" s="56"/>
-    </row>
-    <row r="100" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="48"/>
-      <c r="B100" s="52" t="s">
+    </row>
+    <row r="362" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A362" s="52" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B362" s="52" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C362" s="52" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D362" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A363" s="52" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B363" s="52" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C363" s="52" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D363" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A364" s="48" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B364" s="48" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C364" s="48" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D364" s="49" t="s">
         <v>1846</v>
       </c>
-      <c r="C100" s="56"/>
-    </row>
-    <row r="101" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="49"/>
-      <c r="B101" s="53" t="s">
+    </row>
+    <row r="365" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A365" s="52" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B365" s="52" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C365" s="52" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D365" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A366" s="52" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B366" s="52" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C366" s="52" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D366" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A367" s="46" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B367" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C367" s="47" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D367" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A368" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B368" s="48" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C368" s="48" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D368" s="49" t="s">
         <v>1846</v>
       </c>
-      <c r="C101" s="57"/>
-    </row>
+    </row>
+    <row r="369" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A369" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B369" s="52" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C369" s="52" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D369" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A370" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B370" s="52" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C370" s="52" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D370" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A371" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B371" s="48" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C371" s="48" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D371" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A372" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B372" s="52" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C372" s="52" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D372" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A373" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B373" s="52" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C373" s="52" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D373" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A374" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B374" s="48" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C374" s="48" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D374" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A375" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B375" s="52" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C375" s="52" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D375" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A376" s="52" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B376" s="52" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C376" s="52" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D376" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A377" s="46" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B377" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C377" s="47" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D377" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A378" s="48" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B378" s="48" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C378" s="48" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D378" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A379" s="52" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B379" s="52" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C379" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D379" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A380" s="52" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B380" s="52" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C380" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D380" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A381" s="48" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B381" s="48" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C381" s="48" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D381" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A382" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B382" s="52" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C382" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D382" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A383" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B383" s="52" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C383" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D383" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A384" s="48" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B384" s="48" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C384" s="48" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D384" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A385" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B385" s="52" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C385" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D385" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A386" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B386" s="52" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C386" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D386" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A387" s="48" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B387" s="48" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C387" s="48" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D387" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A388" s="52" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B388" s="52" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C388" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D388" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A389" s="52" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B389" s="52" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C389" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D389" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A390" s="46" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B390" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C390" s="47" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D390" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A391" s="48" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B391" s="48" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C391" s="48" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D391" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A392" s="52" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B392" s="52" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C392" s="52" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D392" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A393" s="52" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B393" s="52" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C393" s="52" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D393" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A394" s="48" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B394" s="48" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C394" s="48" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D394" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A395" s="52" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B395" s="52" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C395" s="52" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D395" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A396" s="52" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B396" s="52" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C396" s="52" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D396" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A397" s="46" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B397" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C397" s="47" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D397" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A398" s="48" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B398" s="48" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C398" s="48" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D398" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A399" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B399" s="52" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C399" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D399" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A400" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B400" s="52" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C400" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D400" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A401" s="48" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B401" s="48" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C401" s="48" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D401" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A402" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B402" s="52" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C402" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D402" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A403" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B403" s="52" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C403" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D403" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A404" s="48" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B404" s="48" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C404" s="48" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D404" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A405" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B405" s="52" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C405" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D405" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A406" s="52" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B406" s="52" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C406" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D406" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A407" s="46" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B407" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C407" s="47" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D407" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A408" s="48" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B408" s="48" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C408" s="48" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D408" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A409" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B409" s="52" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C409" s="52" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D409" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A410" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B410" s="52" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C410" s="52" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D410" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A411" s="48" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B411" s="48" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C411" s="48" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D411" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A412" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B412" s="52" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C412" s="52" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D412" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A413" s="52" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B413" s="52" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C413" s="52" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D413" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A414" s="46" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B414" s="47" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C414" s="47" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D414" s="47" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A415" s="48" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B415" s="48" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C415" s="48" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D415" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A416" s="52" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B416" s="52" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C416" s="52" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D416" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A417" s="52" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B417" s="52" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C417" s="52" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D417" s="53" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/TY_Product_Database.xlsx
+++ b/data/TY_Product_Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanfoo/Documents/Codex/2026-09-07/in/outputs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49048954-40D0-934A-987C-1752C0BEB375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11362356-1029-BB43-A0D6-2229DD9D724A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33620" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33620" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1975">
   <si>
     <t>TY Product Database</t>
   </si>
@@ -6068,6 +6068,9 @@
   </si>
   <si>
     <t>1 Phase / 220V / 50Hz / 3.30kw / 17.7A / 15A Plug</t>
+  </si>
+  <si>
+    <t>Glass Display Chiller</t>
   </si>
   <si>
     <t>1250(W) x 750(D) x 2000(H)</t>
@@ -24910,16 +24913,16 @@
         <v>508</v>
       </c>
       <c r="C116" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D116" s="60" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="E116" s="67" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="F116" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G116" s="69" t="s">
         <v>1677</v>
@@ -24931,7 +24934,7 @@
         <v>1548</v>
       </c>
       <c r="J116" s="60" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -24939,19 +24942,19 @@
         <v>1923</v>
       </c>
       <c r="B117" s="60" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="C117" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D117" s="60" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="E117" s="67" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="F117" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G117" s="69" t="s">
         <v>1677</v>
@@ -24963,7 +24966,7 @@
         <v>1548</v>
       </c>
       <c r="J117" s="60" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -24974,16 +24977,16 @@
         <v>510</v>
       </c>
       <c r="C118" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D118" s="66" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="E118" s="68" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="F118" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G118" s="66" t="s">
         <v>1677</v>
@@ -24995,7 +24998,7 @@
         <v>1548</v>
       </c>
       <c r="J118" s="66" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -25003,19 +25006,19 @@
         <v>1923</v>
       </c>
       <c r="B119" s="66" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="C119" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D119" s="66" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="E119" s="68" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="F119" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G119" s="66" t="s">
         <v>1677</v>
@@ -25027,7 +25030,7 @@
         <v>1548</v>
       </c>
       <c r="J119" s="66" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -25035,19 +25038,19 @@
         <v>1923</v>
       </c>
       <c r="B120" s="66" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="C120" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D120" s="66" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="E120" s="68" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="F120" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G120" s="66" t="s">
         <v>1677</v>
@@ -25059,7 +25062,7 @@
         <v>1548</v>
       </c>
       <c r="J120" s="66" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -25067,19 +25070,19 @@
         <v>1923</v>
       </c>
       <c r="B121" s="66" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="C121" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D121" s="66" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="E121" s="68" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="F121" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G121" s="66" t="s">
         <v>1677</v>
@@ -25091,7 +25094,7 @@
         <v>1548</v>
       </c>
       <c r="J121" s="66" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -25102,16 +25105,16 @@
         <v>515</v>
       </c>
       <c r="C122" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D122" s="66" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="E122" s="68" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="F122" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G122" s="66" t="s">
         <v>1677</v>
@@ -25123,7 +25126,7 @@
         <v>1548</v>
       </c>
       <c r="J122" s="66" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="28" x14ac:dyDescent="0.15">
@@ -25131,19 +25134,19 @@
         <v>1923</v>
       </c>
       <c r="B123" s="66" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="C123" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D123" s="66" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="E123" s="68" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="F123" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G123" s="66" t="s">
         <v>1677</v>
@@ -25155,7 +25158,7 @@
         <v>1548</v>
       </c>
       <c r="J123" s="66" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="42" x14ac:dyDescent="0.15">
@@ -25163,19 +25166,19 @@
         <v>1923</v>
       </c>
       <c r="B124" s="66" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C124" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D124" s="66" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="E124" s="68" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="F124" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G124" s="66" t="s">
         <v>1677</v>
@@ -25187,7 +25190,7 @@
         <v>1548</v>
       </c>
       <c r="J124" s="66" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="42" x14ac:dyDescent="0.15">
@@ -25195,19 +25198,19 @@
         <v>1923</v>
       </c>
       <c r="B125" s="66" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C125" s="60" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D125" s="66" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="E125" s="68" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="F125" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G125" s="66" t="s">
         <v>1677</v>
@@ -25219,7 +25222,7 @@
         <v>1548</v>
       </c>
       <c r="J125" s="66" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="42" x14ac:dyDescent="0.15">
@@ -25227,19 +25230,19 @@
         <v>1923</v>
       </c>
       <c r="B126" s="66" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="C126" s="66" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D126" s="66" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E126" s="68" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="F126" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G126" s="66" t="s">
         <v>1677</v>
@@ -25251,7 +25254,7 @@
         <v>1548</v>
       </c>
       <c r="J126" s="66" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="42" x14ac:dyDescent="0.15">
@@ -25259,19 +25262,19 @@
         <v>1923</v>
       </c>
       <c r="B127" s="66" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="C127" s="66" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D127" s="66" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E127" s="68" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="F127" s="41" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G127" s="66" t="s">
         <v>1677</v>
@@ -25283,7 +25286,7 @@
         <v>1548</v>
       </c>
       <c r="J127" s="66" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="42" x14ac:dyDescent="0.15">
@@ -25291,22 +25294,22 @@
         <v>1923</v>
       </c>
       <c r="B128" s="66" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="C128" s="66" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D128" s="66" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="E128" s="68" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="F128" s="41" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G128" s="66" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H128" s="66" t="s">
         <v>1556</v>
@@ -25315,7 +25318,7 @@
         <v>1548</v>
       </c>
       <c r="J128" s="66" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="42" x14ac:dyDescent="0.15">
@@ -25323,22 +25326,22 @@
         <v>1923</v>
       </c>
       <c r="B129" s="66" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="C129" s="66" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D129" s="66" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="E129" s="68" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="F129" s="41" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G129" s="66" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H129" s="66" t="s">
         <v>1556</v>
@@ -25347,7 +25350,7 @@
         <v>1548</v>
       </c>
       <c r="J129" s="66" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.15">
@@ -25447,17 +25450,17 @@
       <c r="B136" s="60" t="s">
         <v>636</v>
       </c>
-      <c r="C136" s="60" t="s">
-        <v>1321</v>
+      <c r="C136" s="66" t="s">
+        <v>1933</v>
       </c>
       <c r="D136" s="60" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E136" s="60" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F136" s="41" t="s">
         <v>1971</v>
-      </c>
-      <c r="E136" s="60" t="s">
-        <v>1972</v>
-      </c>
-      <c r="F136" s="41" t="s">
-        <v>1970</v>
       </c>
       <c r="G136" s="60" t="s">
         <v>1677</v>
@@ -25469,7 +25472,7 @@
         <v>1548</v>
       </c>
       <c r="J136" s="60" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="56" x14ac:dyDescent="0.15">
@@ -25477,19 +25480,19 @@
         <v>1854</v>
       </c>
       <c r="B137" s="60" t="s">
-        <v>1969</v>
-      </c>
-      <c r="C137" s="60" t="s">
-        <v>1321</v>
+        <v>1970</v>
+      </c>
+      <c r="C137" s="66" t="s">
+        <v>1933</v>
       </c>
       <c r="D137" s="60" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E137" s="60" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F137" s="41" t="s">
         <v>1971</v>
-      </c>
-      <c r="E137" s="60" t="s">
-        <v>1972</v>
-      </c>
-      <c r="F137" s="41" t="s">
-        <v>1970</v>
       </c>
       <c r="G137" s="60" t="s">
         <v>1677</v>
@@ -25501,7 +25504,7 @@
         <v>1548</v>
       </c>
       <c r="J137" s="60" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
   </sheetData>
@@ -28746,7 +28749,7 @@
         <v>1854</v>
       </c>
       <c r="D184" s="53" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29516,7 +29519,7 @@
         <v>1860</v>
       </c>
       <c r="D239" s="53" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29544,7 +29547,7 @@
         <v>1860</v>
       </c>
       <c r="D241" s="53" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29558,7 +29561,7 @@
         <v>1860</v>
       </c>
       <c r="D242" s="53" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29572,7 +29575,7 @@
         <v>1860</v>
       </c>
       <c r="D243" s="53" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29600,21 +29603,21 @@
         <v>1860</v>
       </c>
       <c r="D245" s="53" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A246" s="48" t="s">
+      <c r="A246" s="52" t="s">
         <v>1740</v>
       </c>
-      <c r="B246" s="48" t="s">
-        <v>1848</v>
-      </c>
-      <c r="C246" s="48" t="s">
+      <c r="B246" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C246" s="52" t="s">
         <v>1860</v>
       </c>
-      <c r="D246" s="49" t="s">
-        <v>1846</v>
+      <c r="D246" s="53" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29622,13 +29625,13 @@
         <v>1740</v>
       </c>
       <c r="B247" s="52" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="C247" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D247" s="53" t="s">
-        <v>1847</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -29636,32 +29639,32 @@
         <v>1740</v>
       </c>
       <c r="B248" s="52" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="C248" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D248" s="53" t="s">
-        <v>1847</v>
+        <v>510</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A249" s="48" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B249" s="48" t="s">
+      <c r="A249" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B249" s="52" t="s">
         <v>1845</v>
       </c>
-      <c r="C249" s="48" t="s">
+      <c r="C249" s="52" t="s">
         <v>1860</v>
       </c>
-      <c r="D249" s="49" t="s">
-        <v>1846</v>
+      <c r="D249" s="53" t="s">
+        <v>1942</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="52" t="s">
-        <v>1752</v>
+        <v>1740</v>
       </c>
       <c r="B250" s="52" t="s">
         <v>1845</v>
@@ -29670,12 +29673,12 @@
         <v>1860</v>
       </c>
       <c r="D250" s="53" t="s">
-        <v>1847</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="52" t="s">
-        <v>1752</v>
+        <v>1740</v>
       </c>
       <c r="B251" s="52" t="s">
         <v>1845</v>
@@ -29684,152 +29687,152 @@
         <v>1860</v>
       </c>
       <c r="D251" s="53" t="s">
-        <v>1847</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A252" s="48" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B252" s="48" t="s">
-        <v>1848</v>
-      </c>
-      <c r="C252" s="48" t="s">
+      <c r="A252" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B252" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C252" s="52" t="s">
         <v>1860</v>
       </c>
-      <c r="D252" s="49" t="s">
-        <v>1846</v>
+      <c r="D252" s="53" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="52" t="s">
-        <v>1752</v>
+        <v>1740</v>
       </c>
       <c r="B253" s="52" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="C253" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D253" s="53" t="s">
-        <v>1847</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="52" t="s">
-        <v>1752</v>
+        <v>1740</v>
       </c>
       <c r="B254" s="52" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="C254" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D254" s="53" t="s">
-        <v>1847</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A255" s="48" t="s">
-        <v>1759</v>
-      </c>
-      <c r="B255" s="48" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C255" s="48" t="s">
+      <c r="A255" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B255" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C255" s="52" t="s">
         <v>1860</v>
       </c>
-      <c r="D255" s="49" t="s">
-        <v>1846</v>
+      <c r="D255" s="53" t="s">
+        <v>1957</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="52" t="s">
-        <v>1759</v>
+        <v>1740</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>1861</v>
+        <v>1845</v>
       </c>
       <c r="C256" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D256" s="53" t="s">
-        <v>1847</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="52" t="s">
-        <v>1759</v>
+        <v>1740</v>
       </c>
       <c r="B257" s="52" t="s">
-        <v>1861</v>
+        <v>1845</v>
       </c>
       <c r="C257" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D257" s="53" t="s">
-        <v>1847</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A258" s="48" t="s">
-        <v>1759</v>
-      </c>
-      <c r="B258" s="48" t="s">
-        <v>1862</v>
-      </c>
-      <c r="C258" s="48" t="s">
+      <c r="A258" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B258" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C258" s="52" t="s">
         <v>1860</v>
       </c>
-      <c r="D258" s="49" t="s">
-        <v>1846</v>
+      <c r="D258" s="53" t="s">
+        <v>1963</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="52" t="s">
-        <v>1759</v>
+        <v>1740</v>
       </c>
       <c r="B259" s="52" t="s">
-        <v>1862</v>
+        <v>1845</v>
       </c>
       <c r="C259" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D259" s="53" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A260" s="48" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B260" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C260" s="48" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D260" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A261" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B261" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C261" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D261" s="53" t="s">
         <v>1847</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A260" s="52" t="s">
-        <v>1759</v>
-      </c>
-      <c r="B260" s="52" t="s">
-        <v>1862</v>
-      </c>
-      <c r="C260" s="52" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D260" s="53" t="s">
-        <v>1847</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A261" s="48" t="s">
-        <v>1774</v>
-      </c>
-      <c r="B261" s="48" t="s">
-        <v>1848</v>
-      </c>
-      <c r="C261" s="48" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D261" s="49" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="52" t="s">
-        <v>1774</v>
+        <v>1740</v>
       </c>
       <c r="B262" s="52" t="s">
         <v>1848</v>
@@ -29842,39 +29845,39 @@
       </c>
     </row>
     <row r="263" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A263" s="52" t="s">
-        <v>1774</v>
-      </c>
-      <c r="B263" s="52" t="s">
-        <v>1848</v>
-      </c>
-      <c r="C263" s="52" t="s">
+      <c r="A263" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B263" s="48" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C263" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D263" s="53" t="s">
+      <c r="D263" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A264" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B264" s="52" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C264" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D264" s="53" t="s">
         <v>1847</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A264" s="48" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B264" s="48" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C264" s="48" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D264" s="49" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="52" t="s">
-        <v>1786</v>
+        <v>1752</v>
       </c>
       <c r="B265" s="52" t="s">
-        <v>1863</v>
+        <v>1845</v>
       </c>
       <c r="C265" s="52" t="s">
         <v>1860</v>
@@ -29884,39 +29887,39 @@
       </c>
     </row>
     <row r="266" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A266" s="52" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B266" s="52" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C266" s="52" t="s">
+      <c r="A266" s="48" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B266" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C266" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D266" s="53" t="s">
+      <c r="D266" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A267" s="52" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B267" s="52" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C267" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D267" s="53" t="s">
         <v>1847</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A267" s="48" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B267" s="48" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C267" s="48" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D267" s="49" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="52" t="s">
-        <v>1786</v>
+        <v>1752</v>
       </c>
       <c r="B268" s="52" t="s">
-        <v>1864</v>
+        <v>1848</v>
       </c>
       <c r="C268" s="52" t="s">
         <v>1860</v>
@@ -29926,39 +29929,39 @@
       </c>
     </row>
     <row r="269" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A269" s="52" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B269" s="52" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C269" s="52" t="s">
+      <c r="A269" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B269" s="48" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C269" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D269" s="53" t="s">
+      <c r="D269" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A270" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B270" s="52" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C270" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D270" s="53" t="s">
         <v>1847</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A270" s="48" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B270" s="48" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C270" s="48" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D270" s="49" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="52" t="s">
-        <v>1786</v>
+        <v>1759</v>
       </c>
       <c r="B271" s="52" t="s">
-        <v>1865</v>
+        <v>1861</v>
       </c>
       <c r="C271" s="52" t="s">
         <v>1860</v>
@@ -29968,227 +29971,227 @@
       </c>
     </row>
     <row r="272" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A272" s="52" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B272" s="52" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C272" s="52" t="s">
+      <c r="A272" s="48" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B272" s="48" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C272" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D272" s="53" t="s">
+      <c r="D272" s="49" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A273" s="52" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B273" s="52" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C273" s="52" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D273" s="53" t="s">
         <v>1847</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A273" s="48" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B273" s="48" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C273" s="48" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D273" s="49" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="52" t="s">
-        <v>1793</v>
+        <v>1759</v>
       </c>
       <c r="B274" s="52" t="s">
-        <v>1866</v>
+        <v>1862</v>
       </c>
       <c r="C274" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D274" s="53" t="s">
-        <v>690</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A275" s="52" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B275" s="52" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C275" s="52" t="s">
+      <c r="A275" s="48" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B275" s="48" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C275" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D275" s="53" t="s">
-        <v>694</v>
+      <c r="D275" s="49" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="52" t="s">
-        <v>1793</v>
+        <v>1774</v>
       </c>
       <c r="B276" s="52" t="s">
-        <v>1866</v>
+        <v>1848</v>
       </c>
       <c r="C276" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D276" s="53" t="s">
-        <v>697</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="52" t="s">
-        <v>1793</v>
+        <v>1774</v>
       </c>
       <c r="B277" s="52" t="s">
-        <v>1866</v>
+        <v>1848</v>
       </c>
       <c r="C277" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D277" s="53" t="s">
-        <v>700</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A278" s="52" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B278" s="52" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C278" s="52" t="s">
+      <c r="A278" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B278" s="48" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C278" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D278" s="53" t="s">
-        <v>703</v>
+      <c r="D278" s="49" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="52" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="B279" s="52" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="C279" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D279" s="53" t="s">
-        <v>706</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="52" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="B280" s="52" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="C280" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D280" s="53" t="s">
-        <v>1916</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A281" s="52" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B281" s="52" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C281" s="52" t="s">
+      <c r="A281" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B281" s="48" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C281" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D281" s="53" t="s">
-        <v>1917</v>
+      <c r="D281" s="49" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="52" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="B282" s="52" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="C282" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D282" s="53" t="s">
-        <v>1918</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="52" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="B283" s="52" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="C283" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D283" s="53" t="s">
-        <v>508</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A284" s="52" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B284" s="52" t="s">
-        <v>1866</v>
-      </c>
-      <c r="C284" s="52" t="s">
+      <c r="A284" s="48" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B284" s="48" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C284" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D284" s="53" t="s">
-        <v>1936</v>
+      <c r="D284" s="49" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="52" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="B285" s="52" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="C285" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D285" s="53" t="s">
-        <v>510</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="52" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
       <c r="B286" s="52" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="C286" s="52" t="s">
         <v>1860</v>
       </c>
       <c r="D286" s="53" t="s">
-        <v>1941</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A287" s="52" t="s">
+      <c r="A287" s="48" t="s">
         <v>1793</v>
       </c>
-      <c r="B287" s="52" t="s">
+      <c r="B287" s="48" t="s">
         <v>1866</v>
       </c>
-      <c r="C287" s="52" t="s">
+      <c r="C287" s="48" t="s">
         <v>1860</v>
       </c>
-      <c r="D287" s="53" t="s">
-        <v>1942</v>
+      <c r="D287" s="49" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30202,7 +30205,7 @@
         <v>1860</v>
       </c>
       <c r="D288" s="53" t="s">
-        <v>1946</v>
+        <v>690</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30216,7 +30219,7 @@
         <v>1860</v>
       </c>
       <c r="D289" s="53" t="s">
-        <v>515</v>
+        <v>694</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30230,7 +30233,7 @@
         <v>1860</v>
       </c>
       <c r="D290" s="53" t="s">
-        <v>1951</v>
+        <v>697</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30244,7 +30247,7 @@
         <v>1860</v>
       </c>
       <c r="D291" s="53" t="s">
-        <v>1952</v>
+        <v>700</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30258,7 +30261,7 @@
         <v>1860</v>
       </c>
       <c r="D292" s="53" t="s">
-        <v>1956</v>
+        <v>703</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30272,7 +30275,7 @@
         <v>1860</v>
       </c>
       <c r="D293" s="53" t="s">
-        <v>1957</v>
+        <v>706</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30286,7 +30289,7 @@
         <v>1860</v>
       </c>
       <c r="D294" s="53" t="s">
-        <v>1961</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30300,7 +30303,7 @@
         <v>1860</v>
       </c>
       <c r="D295" s="53" t="s">
-        <v>1962</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -30314,7 +30317,7 @@
         <v>1860</v>
       </c>
       <c r="D296" s="53" t="s">
-        <v>1963</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.15">

--- a/data/TY_Product_Database.xlsx
+++ b/data/TY_Product_Database.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R0e74e33222784fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ex-stock" sheetId="2" r:id="R73c61858c56a492d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specifications" sheetId="3" r:id="Ra7a9fd26ce8b4da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Guide" sheetId="4" r:id="R6fe34dfc04a4427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand Lineup" sheetId="5" r:id="Rc019a082c5c04765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rbd5f8b305c614c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ex-stock" sheetId="2" r:id="R49470ce3c5c24644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specifications" sheetId="3" r:id="R08bb846ca3c045c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Guide" sheetId="4" r:id="R25af92e646cd471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand Lineup" sheetId="5" r:id="R722274d75d5b441d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5413,7 +5413,7 @@
     <x:numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <x:numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </x:numFmts>
-  <x:fonts count="22">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="10"/>
       <x:name val="Arial"/>
@@ -5535,8 +5535,14 @@
       <x:color rgb="FF0F5472"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF425466"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -5646,6 +5652,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDDEFFD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B638B"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -5826,7 +5837,7 @@
     <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="176">
+  <x:cellXfs count="184">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -6335,6 +6346,24 @@
     <x:xf numFmtId="0" fontId="21" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="7">
     <x:cellStyle name="Comma" xfId="1"/>
@@ -6345,9 +6374,53 @@
     <x:cellStyle name="Normal 2" xfId="6"/>
     <x:cellStyle name="Percent" xfId="5"/>
   </x:cellStyles>
-  <x:dxfs count="1">
+  <x:dxfs count="5">
     <x:dxf>
       <x:numFmt numFmtId="30" formatCode="@"/>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB54708"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF1D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB54708"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF1D6"/>
+        </x:patternFill>
+      </x:fill>
     </x:dxf>
   </x:dxfs>
   <x:colors>
@@ -6805,7 +6878,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44eac98f78084072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb01de641c6e94159"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6825,6 +6898,7 @@
     <x:col min="6" max="7" width="18" customWidth="1"/>
     <x:col min="8" max="8" width="38" customWidth="1"/>
     <x:col min="9" max="9" width="12" customWidth="1"/>
+    <x:col min="10" max="10" width="31" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -6855,6 +6929,9 @@
       <x:c r="I1" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
+      <x:c r="J1" s="183" t="str">
+        <x:v>Lifecycle Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="3" t="s">
@@ -7580,6 +7657,9 @@
       <x:c r="I26" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J26" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="6" t="s">
@@ -7609,6 +7689,9 @@
       <x:c r="I27" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J27" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="6" t="s">
@@ -7638,6 +7721,9 @@
       <x:c r="I28" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J28" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="6" t="s">
@@ -7667,6 +7753,9 @@
       <x:c r="I29" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J29" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="6" t="s">
@@ -7696,6 +7785,9 @@
       <x:c r="I30" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J30" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="6" t="s">
@@ -7725,6 +7817,9 @@
       <x:c r="I31" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J31" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="6" t="s">
@@ -7754,6 +7849,9 @@
       <x:c r="I32" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J32" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="6" t="s">
@@ -7783,6 +7881,9 @@
       <x:c r="I33" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J33" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="6" t="s">
@@ -7812,6 +7913,9 @@
       <x:c r="I34" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J34" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
       <x:c r="A35" s="6" t="s">
@@ -7841,6 +7945,9 @@
       <x:c r="I35" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J35" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
       <x:c r="A36" s="6" t="s">
@@ -7870,6 +7977,9 @@
       <x:c r="I36" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J36" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
       <x:c r="A37" s="6" t="s">
@@ -7899,6 +8009,9 @@
       <x:c r="I37" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J37" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
       <x:c r="A38" s="6" t="s">
@@ -7928,6 +8041,9 @@
       <x:c r="I38" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J38" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
       <x:c r="A39" s="6" t="s">
@@ -7957,6 +8073,9 @@
       <x:c r="I39" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J39" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
       <x:c r="A40" s="6" t="s">
@@ -7986,6 +8105,9 @@
       <x:c r="I40" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J40" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
       <x:c r="A41" s="6" t="s">
@@ -8015,6 +8137,9 @@
       <x:c r="I41" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J41" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
       <x:c r="A42" s="6" t="s">
@@ -8044,6 +8169,9 @@
       <x:c r="I42" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J42" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
       <x:c r="A43" s="6" t="s">
@@ -8073,6 +8201,9 @@
       <x:c r="I43" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J43" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
       <x:c r="A44" s="6" t="s">
@@ -8102,6 +8233,9 @@
       <x:c r="I44" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J44" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="24" customHeight="1">
       <x:c r="A45" s="6" t="s">
@@ -8131,6 +8265,9 @@
       <x:c r="I45" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J45" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="24" customHeight="1">
       <x:c r="A46" s="6" t="s">
@@ -8160,6 +8297,9 @@
       <x:c r="I46" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J46" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
       <x:c r="A47" s="6" t="s">
@@ -8189,6 +8329,9 @@
       <x:c r="I47" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J47" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="24" customHeight="1">
       <x:c r="A48" s="6" t="s">
@@ -8218,6 +8361,9 @@
       <x:c r="I48" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J48" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
       <x:c r="A49" s="6" t="s">
@@ -8247,6 +8393,9 @@
       <x:c r="I49" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J49" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="24" customHeight="1">
       <x:c r="A50" s="6" t="s">
@@ -8276,6 +8425,9 @@
       <x:c r="I50" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J50" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
       <x:c r="A51" s="6" t="s">
@@ -8305,6 +8457,9 @@
       <x:c r="I51" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J51" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
       <x:c r="A52" s="6" t="s">
@@ -8334,6 +8489,9 @@
       <x:c r="I52" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J52" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
       <x:c r="A53" s="6" t="s">
@@ -8363,6 +8521,9 @@
       <x:c r="I53" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J53" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="24" customHeight="1">
       <x:c r="A54" s="6" t="s">
@@ -8392,6 +8553,9 @@
       <x:c r="I54" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J54" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
       <x:c r="A55" s="6" t="s">
@@ -8421,6 +8585,9 @@
       <x:c r="I55" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J55" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
       <x:c r="A56" s="6" t="s">
@@ -8450,6 +8617,9 @@
       <x:c r="I56" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J56" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
       <x:c r="A57" s="6" t="s">
@@ -8479,6 +8649,9 @@
       <x:c r="I57" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J57" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="24" customHeight="1">
       <x:c r="A58" s="6" t="s">
@@ -8508,6 +8681,9 @@
       <x:c r="I58" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J58" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
       <x:c r="A59" s="6" t="s">
@@ -8537,6 +8713,9 @@
       <x:c r="I59" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J59" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="24" customHeight="1">
       <x:c r="A60" s="6" t="s">
@@ -8566,6 +8745,9 @@
       <x:c r="I60" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J60" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
       <x:c r="A61" s="6" t="s">
@@ -8595,6 +8777,9 @@
       <x:c r="I61" s="66">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J61" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="24" customHeight="1">
       <x:c r="A62" s="6" t="s">
@@ -8624,6 +8809,9 @@
       <x:c r="I62" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J62" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="24" customHeight="1">
       <x:c r="A63" s="6" t="s">
@@ -8653,6 +8841,9 @@
       <x:c r="I63" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J63" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="24" customHeight="1">
       <x:c r="A64" s="6" t="s">
@@ -8682,6 +8873,9 @@
       <x:c r="I64" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J64" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="24" customHeight="1">
       <x:c r="A65" s="6" t="s">
@@ -8711,6 +8905,9 @@
       <x:c r="I65" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J65" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="24" customHeight="1">
       <x:c r="A66" s="6" t="s">
@@ -8740,6 +8937,9 @@
       <x:c r="I66" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J66" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
       <x:c r="A67" s="6" t="s">
@@ -8769,6 +8969,9 @@
       <x:c r="I67" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J67" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="24" customHeight="1">
       <x:c r="A68" s="6" t="s">
@@ -8798,6 +9001,9 @@
       <x:c r="I68" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J68" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="24" customHeight="1">
       <x:c r="A69" s="6" t="s">
@@ -8827,6 +9033,9 @@
       <x:c r="I69" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J69" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="24" customHeight="1">
       <x:c r="A70" s="6" t="s">
@@ -8856,6 +9065,9 @@
       <x:c r="I70" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J70" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="24" customHeight="1">
       <x:c r="A71" s="6" t="s">
@@ -8885,6 +9097,9 @@
       <x:c r="I71" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J71" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="24" customHeight="1">
       <x:c r="A72" s="6" t="s">
@@ -8914,6 +9129,9 @@
       <x:c r="I72" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J72" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="24" customHeight="1">
       <x:c r="A73" s="6" t="s">
@@ -8943,6 +9161,9 @@
       <x:c r="I73" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J73" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="24" customHeight="1">
       <x:c r="A74" s="6" t="s">
@@ -8972,6 +9193,9 @@
       <x:c r="I74" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J74" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="24" customHeight="1">
       <x:c r="A75" s="6" t="s">
@@ -9001,6 +9225,9 @@
       <x:c r="I75" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J75" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="24" customHeight="1">
       <x:c r="A76" s="6" t="s">
@@ -9030,6 +9257,9 @@
       <x:c r="I76" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J76" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="24" customHeight="1">
       <x:c r="A77" s="6" t="s">
@@ -9059,6 +9289,9 @@
       <x:c r="I77" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J77" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="24" customHeight="1">
       <x:c r="A78" s="6" t="s">
@@ -9088,6 +9321,9 @@
       <x:c r="I78" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J78" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="24" customHeight="1">
       <x:c r="A79" s="6" t="s">
@@ -9117,6 +9353,9 @@
       <x:c r="I79" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J79" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="24" customHeight="1">
       <x:c r="A80" s="6" t="s">
@@ -9146,6 +9385,9 @@
       <x:c r="I80" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J80" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="24" customHeight="1">
       <x:c r="A81" s="6" t="s">
@@ -9175,6 +9417,9 @@
       <x:c r="I81" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J81" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="24" customHeight="1">
       <x:c r="A82" s="6" t="s">
@@ -9204,6 +9449,9 @@
       <x:c r="I82" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J82" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="24" customHeight="1">
       <x:c r="A83" s="6" t="s">
@@ -9233,6 +9481,9 @@
       <x:c r="I83" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J83" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="24" customHeight="1">
       <x:c r="A84" s="6" t="s">
@@ -9262,6 +9513,9 @@
       <x:c r="I84" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J84" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="24" customHeight="1">
       <x:c r="A85" s="6" t="s">
@@ -9726,6 +9980,9 @@
       <x:c r="I100" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J100" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="24" customHeight="1">
       <x:c r="A101" s="6" t="s">
@@ -9755,6 +10012,9 @@
       <x:c r="I101" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J101" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="24" customHeight="1">
       <x:c r="A102" s="6" t="s">
@@ -9784,6 +10044,9 @@
       <x:c r="I102" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J102" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="24" customHeight="1">
       <x:c r="A103" s="6" t="s">
@@ -9813,6 +10076,9 @@
       <x:c r="I103" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J103" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="24" customHeight="1">
       <x:c r="A104" s="6" t="s">
@@ -9842,6 +10108,9 @@
       <x:c r="I104" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J104" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="24" customHeight="1">
       <x:c r="A105" s="6" t="s">
@@ -9871,6 +10140,9 @@
       <x:c r="I105" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J105" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="24" customHeight="1">
       <x:c r="A106" s="6" t="s">
@@ -9900,6 +10172,9 @@
       <x:c r="I106" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J106" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="24" customHeight="1">
       <x:c r="A107" s="6" t="s">
@@ -9958,6 +10233,9 @@
       <x:c r="I108" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J108" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="24" customHeight="1">
       <x:c r="A109" s="6" t="s">
@@ -9987,6 +10265,9 @@
       <x:c r="I109" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J109" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="24" customHeight="1">
       <x:c r="A110" s="6" t="s">
@@ -10016,6 +10297,9 @@
       <x:c r="I110" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J110" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="24" customHeight="1">
       <x:c r="A111" s="6" t="s">
@@ -10045,6 +10329,9 @@
       <x:c r="I111" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J111" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" ht="24" customHeight="1">
       <x:c r="A112" s="6" t="s">
@@ -10074,6 +10361,9 @@
       <x:c r="I112" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J112" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" ht="24" customHeight="1">
       <x:c r="A113" s="6" t="s">
@@ -10103,6 +10393,9 @@
       <x:c r="I113" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J113" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" ht="24" customHeight="1">
       <x:c r="A114" s="6" t="s">
@@ -10132,6 +10425,9 @@
       <x:c r="I114" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J114" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="24" customHeight="1">
       <x:c r="A115" s="6" t="s">
@@ -10161,6 +10457,9 @@
       <x:c r="I115" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J115" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="24" customHeight="1">
       <x:c r="A116" s="6" t="s">
@@ -10190,6 +10489,9 @@
       <x:c r="I116" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J116" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="24" customHeight="1">
       <x:c r="A117" s="6" t="s">
@@ -10219,6 +10521,9 @@
       <x:c r="I117" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J117" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="24" customHeight="1">
       <x:c r="A118" s="6" t="s">
@@ -10248,6 +10553,9 @@
       <x:c r="I118" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J118" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" ht="24" customHeight="1">
       <x:c r="A119" s="6" t="s">
@@ -10277,6 +10585,9 @@
       <x:c r="I119" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J119" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="24" customHeight="1">
       <x:c r="A120" s="6" t="s">
@@ -10306,6 +10617,9 @@
       <x:c r="I120" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J120" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" ht="24" customHeight="1">
       <x:c r="A121" s="6" t="s">
@@ -10335,6 +10649,9 @@
       <x:c r="I121" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J121" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" ht="24" customHeight="1">
       <x:c r="A122" s="6" t="s">
@@ -10364,6 +10681,9 @@
       <x:c r="I122" s="66">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="J122" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" ht="24" customHeight="1">
       <x:c r="A123" s="6" t="s">
@@ -10422,6 +10742,9 @@
       <x:c r="I124" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J124" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" ht="24" customHeight="1">
       <x:c r="A125" s="6" t="s">
@@ -10451,6 +10774,9 @@
       <x:c r="I125" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J125" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="24" customHeight="1">
       <x:c r="A126" s="6" t="s">
@@ -10480,6 +10806,9 @@
       <x:c r="I126" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J126" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" ht="24" customHeight="1">
       <x:c r="A127" s="6" t="s">
@@ -10509,6 +10838,9 @@
       <x:c r="I127" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J127" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" ht="24" customHeight="1">
       <x:c r="A128" s="6" t="s">
@@ -10538,6 +10870,9 @@
       <x:c r="I128" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J128" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="24" customHeight="1">
       <x:c r="A129" s="6" t="s">
@@ -10567,6 +10902,9 @@
       <x:c r="I129" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J129" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="24" customHeight="1">
       <x:c r="A130" s="6" t="s">
@@ -10596,6 +10934,9 @@
       <x:c r="I130" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J130" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="24" customHeight="1">
       <x:c r="A131" s="6" t="s">
@@ -10625,6 +10966,9 @@
       <x:c r="I131" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J131" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" ht="24" customHeight="1">
       <x:c r="A132" s="6" t="s">
@@ -10770,6 +11114,9 @@
       <x:c r="I136" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J136" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="24" customHeight="1">
       <x:c r="A137" s="6" t="s">
@@ -10854,6 +11201,9 @@
       <x:c r="I139" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J139" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="140" ht="24" customHeight="1">
       <x:c r="A140" s="6" t="s">
@@ -10883,6 +11233,9 @@
       <x:c r="I140" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J140" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="141" ht="24" customHeight="1">
       <x:c r="A141" s="6" t="s">
@@ -10912,6 +11265,9 @@
       <x:c r="I141" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J141" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="142" ht="24" customHeight="1">
       <x:c r="A142" s="6" t="s">
@@ -10941,6 +11297,9 @@
       <x:c r="I142" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J142" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="143" ht="24" customHeight="1">
       <x:c r="A143" s="6" t="s">
@@ -10970,6 +11329,9 @@
       <x:c r="I143" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J143" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" ht="24" customHeight="1">
       <x:c r="A144" s="6" t="s">
@@ -10999,6 +11361,9 @@
       <x:c r="I144" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J144" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" ht="24" customHeight="1">
       <x:c r="A145" s="6" t="s">
@@ -11028,6 +11393,9 @@
       <x:c r="I145" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J145" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="24" customHeight="1">
       <x:c r="A146" s="6" t="s">
@@ -11057,6 +11425,9 @@
       <x:c r="I146" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J146" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" ht="24" customHeight="1">
       <x:c r="A147" s="6" t="s">
@@ -11086,6 +11457,9 @@
       <x:c r="I147" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J147" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="148" ht="24" customHeight="1">
       <x:c r="A148" s="6" t="s">
@@ -11115,6 +11489,9 @@
       <x:c r="I148" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J148" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" ht="24" customHeight="1">
       <x:c r="A149" s="6" t="s">
@@ -11144,6 +11521,9 @@
       <x:c r="I149" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J149" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="24" customHeight="1">
       <x:c r="A150" s="6" t="s">
@@ -11173,6 +11553,9 @@
       <x:c r="I150" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J150" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" ht="24" customHeight="1">
       <x:c r="A151" s="6" t="s">
@@ -11199,6 +11582,9 @@
       <x:c r="I151" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J151" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" ht="24" customHeight="1">
       <x:c r="A152" s="6" t="s">
@@ -11225,6 +11611,9 @@
       <x:c r="I152" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J152" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" ht="24" customHeight="1">
       <x:c r="A153" s="6" t="s">
@@ -11251,6 +11640,9 @@
       <x:c r="I153" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J153" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" ht="24" customHeight="1">
       <x:c r="A154" s="6" t="s">
@@ -11277,6 +11669,9 @@
       <x:c r="I154" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J154" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="155" ht="24" customHeight="1">
       <x:c r="A155" s="6" t="s">
@@ -11303,6 +11698,9 @@
       <x:c r="I155" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J155" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="156" ht="24" customHeight="1">
       <x:c r="A156" s="6" t="s">
@@ -11329,6 +11727,9 @@
       <x:c r="I156" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J156" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="157" ht="24" customHeight="1">
       <x:c r="A157" s="6" t="s">
@@ -11355,6 +11756,9 @@
       <x:c r="I157" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J157" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="158" ht="24" customHeight="1">
       <x:c r="A158" s="6" t="s">
@@ -11381,6 +11785,9 @@
       <x:c r="I158" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J158" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="159" ht="24" customHeight="1">
       <x:c r="A159" s="6" t="s">
@@ -11404,6 +11811,9 @@
       <x:c r="I159" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J159" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" ht="24" customHeight="1">
       <x:c r="A160" s="6" t="s">
@@ -11427,6 +11837,9 @@
       <x:c r="I160" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J160" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="161" ht="24" customHeight="1">
       <x:c r="A161" s="6" t="s">
@@ -11453,6 +11866,9 @@
       <x:c r="I161" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J161" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="162" ht="24" customHeight="1">
       <x:c r="A162" s="6" t="s">
@@ -11479,6 +11895,9 @@
       <x:c r="I162" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J162" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="163" ht="24" customHeight="1">
       <x:c r="A163" s="6" t="s">
@@ -11499,6 +11918,9 @@
       <x:c r="I163" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J163" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" ht="24" customHeight="1">
       <x:c r="A164" s="6" t="s">
@@ -11522,6 +11944,9 @@
       <x:c r="I164" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J164" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="165" ht="24" customHeight="1">
       <x:c r="A165" s="6" t="s">
@@ -11545,6 +11970,9 @@
       <x:c r="I165" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J165" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="166" ht="24" customHeight="1">
       <x:c r="A166" s="6" t="s">
@@ -11655,6 +12083,9 @@
       <x:c r="I169" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J169" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="170" ht="24" customHeight="1">
       <x:c r="A170" s="6" t="s">
@@ -11678,6 +12109,9 @@
       <x:c r="I170" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J170" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="171" ht="24" customHeight="1">
       <x:c r="A171" s="6" t="s">
@@ -11701,6 +12135,9 @@
       <x:c r="I171" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J171" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="172" ht="24" customHeight="1">
       <x:c r="A172" s="6" t="s">
@@ -11724,6 +12161,9 @@
       <x:c r="I172" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J172" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" ht="24" customHeight="1">
       <x:c r="A173" s="6" t="s">
@@ -11747,6 +12187,9 @@
       <x:c r="I173" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J173" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" ht="24" customHeight="1">
       <x:c r="A174" s="6" t="s">
@@ -11770,6 +12213,9 @@
       <x:c r="I174" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J174" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="175" ht="24" customHeight="1">
       <x:c r="A175" s="6" t="s">
@@ -11793,6 +12239,9 @@
       <x:c r="I175" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J175" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="176" ht="24" customHeight="1">
       <x:c r="A176" s="6" t="s">
@@ -11819,6 +12268,9 @@
       <x:c r="I176" s="66">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="J176" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="177" ht="24" customHeight="1">
       <x:c r="A177" s="6" t="s">
@@ -11845,6 +12297,9 @@
       <x:c r="I177" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J177" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="178" ht="24" customHeight="1">
       <x:c r="A178" s="6" t="s">
@@ -11871,6 +12326,9 @@
       <x:c r="I178" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J178" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="179" ht="24" customHeight="1">
       <x:c r="A179" s="6" t="s">
@@ -11897,6 +12355,9 @@
       <x:c r="I179" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J179" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="180" ht="24" customHeight="1">
       <x:c r="A180" s="6" t="s">
@@ -11923,6 +12384,9 @@
       <x:c r="I180" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J180" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="181" ht="24" customHeight="1">
       <x:c r="A181" s="6" t="s">
@@ -11949,6 +12413,9 @@
       <x:c r="I181" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J181" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="182" ht="24" customHeight="1">
       <x:c r="A182" s="6" t="s">
@@ -12175,6 +12642,9 @@
       <x:c r="I189" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J189" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="190" ht="24" customHeight="1">
       <x:c r="A190" s="6" t="s">
@@ -12201,6 +12671,9 @@
       <x:c r="I190" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J190" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="191" ht="24" customHeight="1">
       <x:c r="A191" s="6" t="s">
@@ -12224,6 +12697,9 @@
       <x:c r="I191" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J191" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="192" ht="24" customHeight="1">
       <x:c r="A192" s="6" t="s">
@@ -12247,6 +12723,9 @@
       <x:c r="I192" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J192" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="193" ht="24" customHeight="1">
       <x:c r="A193" s="6" t="s">
@@ -12273,6 +12752,9 @@
       <x:c r="I193" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J193" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="194" ht="24" customHeight="1">
       <x:c r="A194" s="6" t="s">
@@ -12296,6 +12778,9 @@
       <x:c r="I194" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J194" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="195" ht="24" customHeight="1">
       <x:c r="A195" s="6" t="s">
@@ -12319,6 +12804,9 @@
       <x:c r="I195" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J195" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" ht="24" customHeight="1">
       <x:c r="A196" s="6" t="s">
@@ -12348,6 +12836,9 @@
       <x:c r="I196" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J196" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="197" ht="24" customHeight="1">
       <x:c r="A197" s="6" t="s">
@@ -12374,6 +12865,9 @@
       <x:c r="I197" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J197" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="198" ht="24" customHeight="1">
       <x:c r="A198" s="6" t="s">
@@ -12397,6 +12891,9 @@
       <x:c r="I198" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J198" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="199" ht="24" customHeight="1">
       <x:c r="A199" s="6" t="s">
@@ -12423,6 +12920,9 @@
       <x:c r="I199" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J199" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="200" ht="24" customHeight="1">
       <x:c r="A200" s="6" t="s">
@@ -12446,6 +12946,9 @@
       <x:c r="I200" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J200" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="201" ht="24" customHeight="1">
       <x:c r="A201" s="6" t="s">
@@ -12475,6 +12978,9 @@
       <x:c r="I201" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J201" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="202" ht="24" customHeight="1">
       <x:c r="A202" s="6" t="s">
@@ -12504,6 +13010,9 @@
       <x:c r="I202" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J202" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="203" ht="24" customHeight="1">
       <x:c r="A203" s="6" t="s">
@@ -12530,6 +13039,9 @@
       <x:c r="I203" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J203" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="204" ht="24" customHeight="1">
       <x:c r="A204" s="6" t="s">
@@ -12559,6 +13071,9 @@
       <x:c r="I204" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J204" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="205" ht="24" customHeight="1">
       <x:c r="A205" s="6" t="s">
@@ -12582,6 +13097,9 @@
       <x:c r="I205" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J205" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="206" ht="24" customHeight="1">
       <x:c r="A206" s="6" t="s">
@@ -12605,6 +13123,9 @@
       <x:c r="I206" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J206" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="207" ht="24" customHeight="1">
       <x:c r="A207" s="6" t="s">
@@ -12628,6 +13149,9 @@
       <x:c r="I207" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J207" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" ht="24" customHeight="1">
       <x:c r="A208" s="6" t="s">
@@ -12654,6 +13178,9 @@
       <x:c r="I208" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J208" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="209" ht="24" customHeight="1">
       <x:c r="A209" s="6" t="s">
@@ -12680,6 +13207,9 @@
       <x:c r="I209" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J209" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" ht="24" customHeight="1">
       <x:c r="A210" s="6" t="s">
@@ -12706,6 +13236,9 @@
       <x:c r="I210" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J210" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="211" ht="24" customHeight="1">
       <x:c r="A211" s="6" t="s">
@@ -12906,6 +13439,9 @@
       <x:c r="I217" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J217" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" ht="24" customHeight="1">
       <x:c r="A218" s="6" t="s">
@@ -12932,6 +13468,9 @@
       <x:c r="I218" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J218" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="219" ht="24" customHeight="1">
       <x:c r="A219" s="6" t="s">
@@ -12958,6 +13497,9 @@
       <x:c r="I219" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J219" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="24" customHeight="1">
       <x:c r="A220" s="6" t="s">
@@ -12984,6 +13526,9 @@
       <x:c r="I220" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J220" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="24" customHeight="1">
       <x:c r="A221" s="6" t="s">
@@ -13010,6 +13555,9 @@
       <x:c r="I221" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J221" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" ht="24" customHeight="1">
       <x:c r="A222" s="6" t="s">
@@ -13033,6 +13581,9 @@
       <x:c r="I222" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J222" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="223" ht="24" customHeight="1">
       <x:c r="A223" s="6" t="s">
@@ -13056,6 +13607,9 @@
       <x:c r="I223" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J223" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="224" ht="24" customHeight="1">
       <x:c r="A224" s="6" t="s">
@@ -13082,6 +13636,9 @@
       <x:c r="I224" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J224" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="225" ht="24" customHeight="1">
       <x:c r="A225" s="6" t="s">
@@ -13137,6 +13694,9 @@
       <x:c r="I226" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J226" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="227" ht="24" customHeight="1">
       <x:c r="A227" s="6" t="s">
@@ -13163,6 +13723,9 @@
       <x:c r="I227" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J227" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="228" ht="24" customHeight="1">
       <x:c r="A228" s="6" t="s">
@@ -13189,6 +13752,9 @@
       <x:c r="I228" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J228" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="229" ht="24" customHeight="1">
       <x:c r="A229" s="6" t="s">
@@ -13215,6 +13781,9 @@
       <x:c r="I229" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J229" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="230" ht="24" customHeight="1">
       <x:c r="A230" s="6" t="s">
@@ -13241,6 +13810,9 @@
       <x:c r="I230" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J230" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="231" ht="24" customHeight="1">
       <x:c r="A231" s="6" t="s">
@@ -13293,6 +13865,9 @@
       <x:c r="I232" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J232" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="233" ht="24" customHeight="1">
       <x:c r="A233" s="6" t="s">
@@ -13319,6 +13894,9 @@
       <x:c r="I233" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J233" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="234" ht="24" customHeight="1">
       <x:c r="A234" s="6" t="s">
@@ -13342,6 +13920,9 @@
       <x:c r="I234" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J234" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="235" ht="24" customHeight="1">
       <x:c r="A235" s="6" t="s">
@@ -13365,6 +13946,9 @@
       <x:c r="I235" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J235" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="236" ht="24" customHeight="1">
       <x:c r="A236" s="6" t="s">
@@ -13483,6 +14067,9 @@
       <x:c r="I240" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J240" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="241" ht="24" customHeight="1">
       <x:c r="A241" s="6" t="s">
@@ -13561,6 +14148,9 @@
       <x:c r="I243" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J243" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="244" ht="24" customHeight="1">
       <x:c r="A244" s="6" t="s">
@@ -13587,6 +14177,9 @@
       <x:c r="I244" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J244" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="245" ht="24" customHeight="1">
       <x:c r="A245" s="6" t="s">
@@ -13613,6 +14206,9 @@
       <x:c r="I245" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J245" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="246" ht="24" customHeight="1">
       <x:c r="A246" s="6" t="s">
@@ -13639,6 +14235,9 @@
       <x:c r="I246" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J246" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="247" ht="24" customHeight="1">
       <x:c r="A247" s="6" t="s">
@@ -13665,6 +14264,9 @@
       <x:c r="I247" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J247" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="248" ht="24" customHeight="1">
       <x:c r="A248" s="6" t="s">
@@ -13691,6 +14293,9 @@
       <x:c r="I248" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J248" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="249" ht="24" customHeight="1">
       <x:c r="A249" s="6" t="s">
@@ -13714,6 +14319,9 @@
       <x:c r="I249" s="66">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="J249" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="250" ht="24" customHeight="1">
       <x:c r="A250" s="6" t="s">
@@ -13737,6 +14345,9 @@
       <x:c r="I250" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J250" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="251" ht="24" customHeight="1">
       <x:c r="A251" s="6" t="s">
@@ -13763,6 +14374,9 @@
       <x:c r="I251" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J251" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="252" ht="24" customHeight="1">
       <x:c r="A252" s="6" t="s">
@@ -13789,6 +14403,9 @@
       <x:c r="I252" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J252" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="253" ht="24" customHeight="1">
       <x:c r="A253" s="6" t="s">
@@ -14012,6 +14629,9 @@
       <x:c r="I260" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J260" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="261" ht="24" customHeight="1">
       <x:c r="A261" s="6" t="s">
@@ -14038,6 +14658,9 @@
       <x:c r="I261" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J261" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="262" ht="24" customHeight="1">
       <x:c r="A262" s="6" t="s">
@@ -14061,6 +14684,9 @@
       <x:c r="I262" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J262" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="263" ht="24" customHeight="1">
       <x:c r="A263" s="6" t="s">
@@ -14084,6 +14710,9 @@
       <x:c r="I263" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J263" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="264" ht="24" customHeight="1">
       <x:c r="A264" s="6" t="s">
@@ -14110,6 +14739,9 @@
       <x:c r="I264" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J264" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="265" ht="24" customHeight="1">
       <x:c r="A265" s="6" t="s">
@@ -14136,6 +14768,9 @@
       <x:c r="I265" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J265" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="266" ht="24" customHeight="1">
       <x:c r="A266" s="6" t="s">
@@ -14162,6 +14797,9 @@
       <x:c r="I266" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J266" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="267" ht="24" customHeight="1">
       <x:c r="A267" s="6" t="s">
@@ -14188,6 +14826,9 @@
       <x:c r="I267" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J267" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="268" ht="24" customHeight="1">
       <x:c r="A268" s="6" t="s">
@@ -14214,6 +14855,9 @@
       <x:c r="I268" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J268" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="269" ht="24" customHeight="1">
       <x:c r="A269" s="6" t="s">
@@ -14947,6 +15591,9 @@
       <x:c r="I300" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J300" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="301" ht="24" customHeight="1">
       <x:c r="A301" s="6" t="s">
@@ -14970,6 +15617,9 @@
       <x:c r="I301" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J301" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="302" ht="24" customHeight="1">
       <x:c r="A302" s="6" t="s">
@@ -14996,6 +15646,9 @@
       <x:c r="I302" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J302" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="303" ht="24" customHeight="1">
       <x:c r="A303" s="6" t="s">
@@ -15022,6 +15675,9 @@
       <x:c r="I303" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J303" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="304" ht="24" customHeight="1">
       <x:c r="A304" s="6" t="s">
@@ -15048,6 +15704,9 @@
       <x:c r="I304" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J304" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="305" ht="24" customHeight="1">
       <x:c r="A305" s="6" t="s">
@@ -15077,6 +15736,9 @@
       <x:c r="I305" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J305" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="306" ht="24" customHeight="1">
       <x:c r="A306" s="6" t="s">
@@ -15106,6 +15768,9 @@
       <x:c r="I306" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J306" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="307" ht="24" customHeight="1">
       <x:c r="A307" s="6" t="s">
@@ -15187,6 +15852,9 @@
       <x:c r="I309" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J309" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="310" ht="24" customHeight="1">
       <x:c r="A310" s="6" t="s">
@@ -15239,6 +15907,9 @@
       <x:c r="I311" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J311" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="312" ht="24" customHeight="1">
       <x:c r="A312" s="6" t="s">
@@ -15291,6 +15962,9 @@
       <x:c r="I313" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J313" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="314" ht="24" customHeight="1">
       <x:c r="A314" s="6" t="s">
@@ -15314,6 +15988,9 @@
       <x:c r="I314" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J314" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="315" ht="24" customHeight="1">
       <x:c r="A315" s="6" t="s">
@@ -15337,6 +16014,9 @@
       <x:c r="I315" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J315" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="316" ht="24" customHeight="1">
       <x:c r="A316" s="6" t="s">
@@ -15360,6 +16040,9 @@
       <x:c r="I316" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J316" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="317" ht="24" customHeight="1">
       <x:c r="A317" s="6" t="s">
@@ -15383,6 +16066,9 @@
       <x:c r="I317" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J317" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="318" ht="24" customHeight="1">
       <x:c r="A318" s="6" t="s">
@@ -15409,6 +16095,9 @@
       <x:c r="I318" s="66">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="J318" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="319" ht="24" customHeight="1">
       <x:c r="A319" s="6" t="s">
@@ -15435,6 +16124,9 @@
       <x:c r="I319" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J319" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="320" ht="24" customHeight="1">
       <x:c r="A320" s="6" t="s">
@@ -15461,6 +16153,9 @@
       <x:c r="I320" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J320" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="321" ht="24" customHeight="1">
       <x:c r="A321" s="6" t="s">
@@ -15487,6 +16182,9 @@
       <x:c r="I321" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J321" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="322" ht="24" customHeight="1">
       <x:c r="A322" s="6" t="s">
@@ -15513,6 +16211,9 @@
       <x:c r="I322" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J322" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="323" ht="24" customHeight="1">
       <x:c r="A323" s="6" t="s">
@@ -15539,6 +16240,9 @@
       <x:c r="I323" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J323" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="324" ht="24" customHeight="1">
       <x:c r="A324" s="6" t="s">
@@ -15565,6 +16269,9 @@
       <x:c r="I324" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J324" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="325" ht="24" customHeight="1">
       <x:c r="A325" s="6" t="s">
@@ -15594,6 +16301,9 @@
       <x:c r="I325" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J325" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="326" ht="24" customHeight="1">
       <x:c r="A326" s="6" t="s">
@@ -15794,6 +16504,9 @@
       <x:c r="I332" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J332" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="333" ht="24" customHeight="1">
       <x:c r="A333" s="6" t="s">
@@ -15820,6 +16533,9 @@
       <x:c r="I333" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J333" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="334" ht="24" customHeight="1">
       <x:c r="A334" s="6" t="s">
@@ -15849,6 +16565,9 @@
       <x:c r="I334" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J334" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="335" ht="24" customHeight="1">
       <x:c r="A335" s="6" t="s">
@@ -15878,6 +16597,9 @@
       <x:c r="I335" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J335" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="336" ht="24" customHeight="1">
       <x:c r="A336" s="6" t="s">
@@ -15901,6 +16623,9 @@
       <x:c r="I336" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J336" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="337" ht="24" customHeight="1">
       <x:c r="A337" s="6" t="s">
@@ -15930,6 +16655,9 @@
       <x:c r="I337" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J337" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="338" ht="24" customHeight="1">
       <x:c r="A338" s="6" t="s">
@@ -15976,6 +16704,9 @@
       <x:c r="I339" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J339" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="340" ht="24" customHeight="1">
       <x:c r="A340" s="6" t="s">
@@ -16002,6 +16733,9 @@
       <x:c r="I340" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J340" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="341" ht="24" customHeight="1">
       <x:c r="A341" s="6" t="s">
@@ -16025,6 +16759,9 @@
       <x:c r="I341" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J341" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="342" ht="24" customHeight="1">
       <x:c r="A342" s="6" t="s">
@@ -16048,6 +16785,9 @@
       <x:c r="I342" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J342" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="343" ht="24" customHeight="1">
       <x:c r="A343" s="6" t="s">
@@ -16074,6 +16814,9 @@
       <x:c r="I343" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J343" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="344" ht="24" customHeight="1">
       <x:c r="A344" s="6" t="s">
@@ -16097,6 +16840,9 @@
       <x:c r="I344" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J344" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="345" ht="24" customHeight="1">
       <x:c r="A345" s="6" t="s">
@@ -16126,6 +16872,9 @@
       <x:c r="I345" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J345" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="346" ht="24" customHeight="1">
       <x:c r="A346" s="6" t="s">
@@ -16155,6 +16904,9 @@
       <x:c r="I346" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J346" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="347" ht="24" customHeight="1">
       <x:c r="A347" s="6" t="s">
@@ -16181,6 +16933,9 @@
       <x:c r="I347" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J347" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="348" ht="24" customHeight="1">
       <x:c r="A348" s="6" t="s">
@@ -16210,6 +16965,9 @@
       <x:c r="I348" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J348" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="349" ht="24" customHeight="1">
       <x:c r="A349" s="6" t="s">
@@ -16236,6 +16994,9 @@
       <x:c r="I349" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J349" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="350" ht="24" customHeight="1">
       <x:c r="A350" s="6" t="s">
@@ -16262,6 +17023,9 @@
       <x:c r="I350" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J350" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="351" ht="24" customHeight="1">
       <x:c r="A351" s="6" t="s">
@@ -16288,6 +17052,9 @@
       <x:c r="I351" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J351" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="352" ht="24" customHeight="1">
       <x:c r="A352" s="6" t="s">
@@ -16659,6 +17426,9 @@
       <x:c r="I367" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J367" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="368" ht="24" customHeight="1">
       <x:c r="A368" s="6" t="s">
@@ -16685,6 +17455,9 @@
       <x:c r="I368" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J368" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="369" ht="24" customHeight="1">
       <x:c r="A369" s="6" t="s">
@@ -16711,6 +17484,9 @@
       <x:c r="I369" s="66">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="J369" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="370" ht="24" customHeight="1">
       <x:c r="A370" s="6" t="s">
@@ -16737,6 +17513,9 @@
       <x:c r="I370" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J370" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="371" ht="24" customHeight="1">
       <x:c r="A371" s="6" t="s">
@@ -16763,6 +17542,9 @@
       <x:c r="I371" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J371" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="372" ht="24" customHeight="1">
       <x:c r="A372" s="6" t="s">
@@ -16789,6 +17571,9 @@
       <x:c r="I372" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J372" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="373" ht="24" customHeight="1">
       <x:c r="A373" s="6" t="s">
@@ -16815,6 +17600,9 @@
       <x:c r="I373" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J373" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="374" ht="24" customHeight="1">
       <x:c r="A374" s="6" t="s">
@@ -16841,6 +17629,9 @@
       <x:c r="I374" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J374" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="375" ht="24" customHeight="1">
       <x:c r="A375" s="6" t="s">
@@ -16867,6 +17658,9 @@
       <x:c r="I375" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J375" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="376" ht="24" customHeight="1">
       <x:c r="A376" s="6" t="s">
@@ -16893,6 +17687,9 @@
       <x:c r="I376" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J376" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="377" ht="24" customHeight="1">
       <x:c r="A377" s="6" t="s">
@@ -16916,6 +17713,9 @@
       <x:c r="I377" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J377" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="378" ht="24" customHeight="1">
       <x:c r="A378" s="6" t="s">
@@ -16939,6 +17739,9 @@
       <x:c r="I378" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J378" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="379" ht="24" customHeight="1">
       <x:c r="A379" s="6" t="s">
@@ -16965,6 +17768,9 @@
       <x:c r="I379" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J379" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="380" ht="24" customHeight="1">
       <x:c r="A380" s="6" t="s">
@@ -16988,6 +17794,9 @@
       <x:c r="I380" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J380" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="381" ht="24" customHeight="1">
       <x:c r="A381" s="6" t="s">
@@ -17011,6 +17820,9 @@
       <x:c r="I381" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J381" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="382" ht="24" customHeight="1">
       <x:c r="A382" s="6" t="s">
@@ -17034,6 +17846,9 @@
       <x:c r="I382" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J382" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="383" ht="24" customHeight="1">
       <x:c r="A383" s="6" t="s">
@@ -17060,6 +17875,9 @@
       <x:c r="I383" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J383" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="384" ht="24" customHeight="1">
       <x:c r="A384" s="6" t="s">
@@ -17083,6 +17901,9 @@
       <x:c r="I384" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J384" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="385" ht="24" customHeight="1">
       <x:c r="A385" s="6" t="s">
@@ -17109,6 +17930,9 @@
       <x:c r="I385" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J385" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="386" ht="24" customHeight="1">
       <x:c r="A386" s="6" t="s">
@@ -17132,6 +17956,9 @@
       <x:c r="I386" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J386" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="387" ht="24" customHeight="1">
       <x:c r="A387" s="6" t="s">
@@ -17155,6 +17982,9 @@
       <x:c r="I387" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J387" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="388" ht="24" customHeight="1">
       <x:c r="A388" s="6" t="s">
@@ -17181,6 +18011,9 @@
       <x:c r="I388" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J388" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="389" ht="24" customHeight="1">
       <x:c r="A389" s="6" t="s">
@@ -17207,6 +18040,9 @@
       <x:c r="I389" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J389" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="390" ht="24" customHeight="1">
       <x:c r="A390" s="6" t="s">
@@ -17233,6 +18069,9 @@
       <x:c r="I390" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J390" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="391" ht="24" customHeight="1">
       <x:c r="A391" s="6" t="s">
@@ -17256,6 +18095,9 @@
       <x:c r="I391" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J391" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="392" ht="24" customHeight="1">
       <x:c r="A392" s="6" t="s">
@@ -17282,6 +18124,9 @@
       <x:c r="I392" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J392" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="393" ht="24" customHeight="1">
       <x:c r="A393" s="6" t="s">
@@ -17308,6 +18153,9 @@
       <x:c r="I393" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J393" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="394" ht="24" customHeight="1">
       <x:c r="A394" s="6" t="s">
@@ -17331,6 +18179,9 @@
       <x:c r="I394" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J394" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="395" ht="24" customHeight="1">
       <x:c r="A395" s="6" t="s">
@@ -17357,6 +18208,9 @@
       <x:c r="I395" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J395" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="396" ht="24" customHeight="1">
       <x:c r="A396" s="6" t="s">
@@ -17380,6 +18234,9 @@
       <x:c r="I396" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J396" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="397" ht="24" customHeight="1">
       <x:c r="A397" s="6" t="s">
@@ -17406,6 +18263,9 @@
       <x:c r="I397" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J397" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="398" ht="24" customHeight="1">
       <x:c r="A398" s="6" t="s">
@@ -17432,6 +18292,9 @@
       <x:c r="I398" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J398" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="399" ht="24" customHeight="1">
       <x:c r="A399" s="6" t="s">
@@ -17455,6 +18318,9 @@
       <x:c r="I399" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J399" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="400" ht="24" customHeight="1">
       <x:c r="A400" s="6" t="s">
@@ -17481,6 +18347,9 @@
       <x:c r="I400" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J400" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="401" ht="24" customHeight="1">
       <x:c r="A401" s="6" t="s">
@@ -17507,6 +18376,9 @@
       <x:c r="I401" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J401" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="402" ht="24" customHeight="1">
       <x:c r="A402" s="6" t="s">
@@ -17536,6 +18408,9 @@
       <x:c r="I402" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J402" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="403" ht="24" customHeight="1">
       <x:c r="A403" s="6" t="s">
@@ -17565,6 +18440,9 @@
       <x:c r="I403" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J403" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="404" ht="24" customHeight="1">
       <x:c r="A404" s="6" t="s">
@@ -17594,6 +18472,9 @@
       <x:c r="I404" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J404" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="405" ht="24" customHeight="1">
       <x:c r="A405" s="6" t="s">
@@ -17623,6 +18504,9 @@
       <x:c r="I405" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J405" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="406" ht="24" customHeight="1">
       <x:c r="A406" s="6" t="s">
@@ -17652,6 +18536,9 @@
       <x:c r="I406" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J406" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="407" ht="24" customHeight="1">
       <x:c r="A407" s="6" t="s">
@@ -17678,6 +18565,9 @@
       <x:c r="I407" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J407" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="408" ht="24" customHeight="1">
       <x:c r="A408" s="6" t="s">
@@ -17707,6 +18597,9 @@
       <x:c r="I408" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J408" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="409" ht="24" customHeight="1">
       <x:c r="A409" s="6" t="s">
@@ -17736,6 +18629,9 @@
       <x:c r="I409" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J409" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="410" ht="24" customHeight="1">
       <x:c r="A410" s="6" t="s">
@@ -17765,6 +18661,9 @@
       <x:c r="I410" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J410" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="411" ht="24" customHeight="1">
       <x:c r="A411" s="6" t="s">
@@ -17791,6 +18690,9 @@
       <x:c r="I411" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J411" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="412" ht="24" customHeight="1">
       <x:c r="A412" s="6" t="s">
@@ -17817,6 +18719,9 @@
       <x:c r="I412" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J412" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="413" ht="24" customHeight="1">
       <x:c r="A413" s="6" t="s">
@@ -17843,6 +18748,9 @@
       <x:c r="I413" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J413" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="414" ht="24" customHeight="1">
       <x:c r="A414" s="6" t="s">
@@ -17869,6 +18777,9 @@
       <x:c r="I414" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J414" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="415" ht="24" customHeight="1">
       <x:c r="A415" s="6" t="s">
@@ -17892,6 +18803,9 @@
       <x:c r="I415" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J415" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="416" ht="24" customHeight="1">
       <x:c r="A416" s="6" t="s">
@@ -17918,6 +18832,9 @@
       <x:c r="I416" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J416" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="417" ht="24" customHeight="1">
       <x:c r="A417" s="6" t="s">
@@ -17944,6 +18861,9 @@
       <x:c r="I417" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J417" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="418" ht="24" customHeight="1">
       <x:c r="A418" s="6" t="s">
@@ -17970,6 +18890,9 @@
       <x:c r="I418" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J418" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="419" ht="24" customHeight="1">
       <x:c r="A419" s="6" t="s">
@@ -17996,6 +18919,9 @@
       <x:c r="I419" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J419" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="420" ht="24" customHeight="1">
       <x:c r="A420" s="6" t="s">
@@ -18022,6 +18948,9 @@
       <x:c r="I420" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J420" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="421" ht="24" customHeight="1">
       <x:c r="A421" s="6" t="s">
@@ -18048,6 +18977,9 @@
       <x:c r="I421" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J421" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="422" ht="24" customHeight="1">
       <x:c r="A422" s="6" t="s">
@@ -18074,6 +19006,9 @@
       <x:c r="I422" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J422" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="423" ht="24" customHeight="1">
       <x:c r="A423" s="6" t="s">
@@ -18100,6 +19035,9 @@
       <x:c r="I423" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J423" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="424" ht="24" customHeight="1">
       <x:c r="A424" s="6" t="s">
@@ -18126,6 +19064,9 @@
       <x:c r="I424" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J424" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="425" ht="24" customHeight="1">
       <x:c r="A425" s="6" t="s">
@@ -18149,6 +19090,9 @@
       <x:c r="I425" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J425" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="426" ht="24" customHeight="1">
       <x:c r="A426" s="6" t="s">
@@ -18175,6 +19119,9 @@
       <x:c r="I426" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J426" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="427" ht="24" customHeight="1">
       <x:c r="A427" s="6" t="s">
@@ -18201,6 +19148,9 @@
       <x:c r="I427" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J427" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="428" ht="24" customHeight="1">
       <x:c r="A428" s="6" t="s">
@@ -18227,6 +19177,9 @@
       <x:c r="I428" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J428" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="429" ht="24" customHeight="1">
       <x:c r="A429" s="6" t="s">
@@ -18253,6 +19206,9 @@
       <x:c r="I429" s="66">
         <x:v>7</x:v>
       </x:c>
+      <x:c r="J429" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="430" ht="24" customHeight="1">
       <x:c r="A430" s="6" t="s">
@@ -18276,6 +19232,9 @@
       <x:c r="I430" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J430" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="431" ht="24" customHeight="1">
       <x:c r="A431" s="6" t="s">
@@ -18299,6 +19258,9 @@
       <x:c r="I431" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J431" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="432" ht="24" customHeight="1">
       <x:c r="A432" s="6" t="s">
@@ -18322,6 +19284,9 @@
       <x:c r="I432" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J432" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="433" ht="24" customHeight="1">
       <x:c r="A433" s="6" t="s">
@@ -18348,6 +19313,9 @@
       <x:c r="I433" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J433" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="434" ht="24" customHeight="1">
       <x:c r="A434" s="6" t="s">
@@ -18371,6 +19339,9 @@
       <x:c r="I434" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J434" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="435" ht="24" customHeight="1">
       <x:c r="A435" s="6" t="s">
@@ -18394,6 +19365,9 @@
       <x:c r="I435" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J435" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="436" ht="24" customHeight="1">
       <x:c r="A436" s="6" t="s">
@@ -18420,6 +19394,9 @@
       <x:c r="I436" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J436" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="437" ht="24" customHeight="1">
       <x:c r="A437" s="6" t="s">
@@ -18443,6 +19420,9 @@
       <x:c r="I437" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J437" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="438" ht="24" customHeight="1">
       <x:c r="A438" s="6" t="s">
@@ -18469,6 +19449,9 @@
       <x:c r="I438" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J438" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="439" ht="24" customHeight="1">
       <x:c r="A439" s="6" t="s">
@@ -18495,6 +19478,9 @@
       <x:c r="I439" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J439" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="440" ht="24" customHeight="1">
       <x:c r="A440" s="6" t="s">
@@ -18521,6 +19507,9 @@
       <x:c r="I440" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J440" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="441" ht="24" customHeight="1">
       <x:c r="A441" s="6" t="s">
@@ -18544,6 +19533,9 @@
       <x:c r="I441" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J441" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="442" ht="24" customHeight="1">
       <x:c r="A442" s="6" t="s">
@@ -18570,6 +19562,9 @@
       <x:c r="I442" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J442" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="443" ht="24" customHeight="1">
       <x:c r="A443" s="6" t="s">
@@ -18596,6 +19591,9 @@
       <x:c r="I443" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J443" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="444" ht="24" customHeight="1">
       <x:c r="A444" s="6" t="s">
@@ -18619,6 +19617,9 @@
       <x:c r="I444" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J444" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="445" ht="24" customHeight="1">
       <x:c r="A445" s="6" t="s">
@@ -18645,6 +19646,9 @@
       <x:c r="I445" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J445" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="446" ht="24" customHeight="1">
       <x:c r="A446" s="6" t="s">
@@ -18671,6 +19675,9 @@
       <x:c r="I446" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J446" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="447" ht="24" customHeight="1">
       <x:c r="A447" s="6" t="s">
@@ -18697,6 +19704,9 @@
       <x:c r="I447" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J447" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="448" ht="24" customHeight="1">
       <x:c r="A448" s="6" t="s">
@@ -18723,6 +19733,9 @@
       <x:c r="I448" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J448" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="449" ht="24" customHeight="1">
       <x:c r="A449" s="6" t="s">
@@ -18752,6 +19765,9 @@
       <x:c r="I449" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J449" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="450" ht="24" customHeight="1">
       <x:c r="A450" s="6" t="s">
@@ -18781,6 +19797,9 @@
       <x:c r="I450" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J450" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="451" ht="24" customHeight="1">
       <x:c r="A451" s="6" t="s">
@@ -18836,6 +19855,9 @@
       <x:c r="I452" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J452" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="453" ht="24" customHeight="1">
       <x:c r="A453" s="6" t="s">
@@ -18891,6 +19913,9 @@
       <x:c r="I454" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J454" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="455" ht="24" customHeight="1">
       <x:c r="A455" s="6" t="s">
@@ -18920,6 +19945,9 @@
       <x:c r="I455" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J455" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="456" ht="24" customHeight="1">
       <x:c r="A456" s="6" t="s">
@@ -18946,6 +19974,9 @@
       <x:c r="I456" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J456" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="457" ht="24" customHeight="1">
       <x:c r="A457" s="6" t="s">
@@ -18966,6 +19997,9 @@
       <x:c r="I457" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J457" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="458" ht="24" customHeight="1">
       <x:c r="A458" s="6" t="s">
@@ -18986,6 +20020,9 @@
       <x:c r="I458" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J458" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="459" ht="24" customHeight="1">
       <x:c r="A459" s="6" t="s">
@@ -19006,6 +20043,9 @@
       <x:c r="I459" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J459" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="460" ht="24" customHeight="1">
       <x:c r="A460" s="6" t="s">
@@ -19032,6 +20072,9 @@
       <x:c r="I460" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J460" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="461" ht="24" customHeight="1">
       <x:c r="A461" s="6" t="s">
@@ -19055,6 +20098,9 @@
       <x:c r="I461" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J461" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="462" ht="24" customHeight="1">
       <x:c r="A462" s="6" t="s">
@@ -19081,6 +20127,9 @@
       <x:c r="I462" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J462" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="463" ht="24" customHeight="1">
       <x:c r="A463" s="6" t="s">
@@ -19107,6 +20156,9 @@
       <x:c r="I463" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J463" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="464" ht="24" customHeight="1">
       <x:c r="A464" s="6" t="s">
@@ -19130,6 +20182,9 @@
       <x:c r="I464" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J464" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="465" ht="24" customHeight="1">
       <x:c r="A465" s="6" t="s">
@@ -19153,6 +20208,9 @@
       <x:c r="I465" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J465" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="466" ht="24" customHeight="1">
       <x:c r="A466" s="6" t="s">
@@ -19176,6 +20234,9 @@
       <x:c r="I466" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J466" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="467" ht="24" customHeight="1">
       <x:c r="A467" s="6" t="s">
@@ -19199,6 +20260,9 @@
       <x:c r="I467" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J467" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="468" ht="24" customHeight="1">
       <x:c r="A468" s="6" t="s">
@@ -19225,6 +20289,9 @@
       <x:c r="I468" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J468" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="469" ht="24" customHeight="1">
       <x:c r="A469" s="6" t="s">
@@ -19251,6 +20318,9 @@
       <x:c r="I469" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J469" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="470" ht="24" customHeight="1">
       <x:c r="A470" s="6" t="s">
@@ -19277,6 +20347,9 @@
       <x:c r="I470" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J470" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="471" ht="24" customHeight="1">
       <x:c r="A471" s="6" t="s">
@@ -19300,6 +20373,9 @@
       <x:c r="I471" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J471" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="472" ht="24" customHeight="1">
       <x:c r="A472" s="6" t="s">
@@ -19323,6 +20399,9 @@
       <x:c r="I472" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J472" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="473" ht="24" customHeight="1">
       <x:c r="A473" s="6" t="s">
@@ -19346,6 +20425,9 @@
       <x:c r="I473" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J473" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="474" ht="24" customHeight="1">
       <x:c r="A474" s="6" t="s">
@@ -19372,6 +20454,9 @@
       <x:c r="I474" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J474" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="475" ht="24" customHeight="1">
       <x:c r="A475" s="6" t="s">
@@ -19398,6 +20483,9 @@
       <x:c r="I475" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J475" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="476" ht="24" customHeight="1">
       <x:c r="A476" s="6" t="s">
@@ -19424,6 +20512,9 @@
       <x:c r="I476" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J476" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="477" ht="24" customHeight="1">
       <x:c r="A477" s="6" t="s">
@@ -19450,6 +20541,9 @@
       <x:c r="I477" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J477" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="478" ht="24" customHeight="1">
       <x:c r="A478" s="6" t="s">
@@ -19476,6 +20570,9 @@
       <x:c r="I478" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J478" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="479" ht="24" customHeight="1">
       <x:c r="A479" s="6" t="s">
@@ -19502,6 +20599,9 @@
       <x:c r="I479" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J479" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="480" ht="24" customHeight="1">
       <x:c r="A480" s="6" t="s">
@@ -19528,6 +20628,9 @@
       <x:c r="I480" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J480" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="481" ht="24" customHeight="1">
       <x:c r="A481" s="6" t="s">
@@ -19551,6 +20654,9 @@
       <x:c r="I481" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J481" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="482" ht="24" customHeight="1">
       <x:c r="A482" s="6" t="s">
@@ -19574,6 +20680,9 @@
       <x:c r="I482" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J482" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="483" ht="24" customHeight="1">
       <x:c r="A483" s="6" t="s">
@@ -19600,6 +20709,9 @@
       <x:c r="I483" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J483" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="484" ht="24" customHeight="1">
       <x:c r="A484" s="6" t="s">
@@ -19623,6 +20735,9 @@
       <x:c r="I484" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J484" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="485" ht="24" customHeight="1">
       <x:c r="A485" s="6" t="s">
@@ -19649,6 +20764,9 @@
       <x:c r="I485" s="66">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J485" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="486" ht="24" customHeight="1">
       <x:c r="A486" s="6" t="s">
@@ -19672,6 +20790,9 @@
       <x:c r="I486" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J486" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="487" ht="24" customHeight="1">
       <x:c r="A487" s="6" t="s">
@@ -19695,6 +20816,9 @@
       <x:c r="I487" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J487" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="488" ht="24" customHeight="1">
       <x:c r="A488" s="6" t="s">
@@ -19721,6 +20845,9 @@
       <x:c r="I488" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J488" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="489" ht="24" customHeight="1">
       <x:c r="A489" s="6" t="s">
@@ -19747,6 +20874,9 @@
       <x:c r="I489" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J489" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="490" ht="24" customHeight="1">
       <x:c r="A490" s="6" t="s">
@@ -19773,6 +20903,9 @@
       <x:c r="I490" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J490" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="491" ht="24" customHeight="1">
       <x:c r="A491" s="6" t="s">
@@ -19799,6 +20932,9 @@
       <x:c r="I491" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J491" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="492" ht="24" customHeight="1">
       <x:c r="A492" s="6" t="s">
@@ -19825,6 +20961,9 @@
       <x:c r="I492" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J492" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="493" ht="24" customHeight="1">
       <x:c r="A493" s="6" t="s">
@@ -19851,6 +20990,9 @@
       <x:c r="I493" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J493" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="494" ht="24" customHeight="1">
       <x:c r="A494" s="6" t="s">
@@ -19877,6 +21019,9 @@
       <x:c r="I494" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J494" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="495" ht="24" customHeight="1">
       <x:c r="A495" s="6" t="s">
@@ -19900,6 +21045,9 @@
       <x:c r="I495" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J495" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="496" ht="24" customHeight="1">
       <x:c r="A496" s="6" t="s">
@@ -19926,6 +21074,9 @@
       <x:c r="I496" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J496" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="497" ht="24" customHeight="1">
       <x:c r="A497" s="6" t="s">
@@ -19949,6 +21100,9 @@
       <x:c r="I497" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J497" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="498" ht="24" customHeight="1">
       <x:c r="A498" s="6" t="s">
@@ -19975,6 +21129,9 @@
       <x:c r="I498" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J498" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="499" ht="24" customHeight="1">
       <x:c r="A499" s="6" t="s">
@@ -19998,6 +21155,9 @@
       <x:c r="I499" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J499" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="500" ht="24" customHeight="1">
       <x:c r="A500" s="6" t="s">
@@ -20021,6 +21181,9 @@
       <x:c r="I500" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J500" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="501" ht="24" customHeight="1">
       <x:c r="A501" s="6" t="s">
@@ -20047,6 +21210,9 @@
       <x:c r="I501" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J501" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="502" ht="24" customHeight="1">
       <x:c r="A502" s="6" t="s">
@@ -20073,6 +21239,9 @@
       <x:c r="I502" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J502" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="503" ht="24" customHeight="1">
       <x:c r="A503" s="6" t="s">
@@ -20096,6 +21265,9 @@
       <x:c r="I503" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J503" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="504" ht="24" customHeight="1">
       <x:c r="A504" s="6" t="s">
@@ -20122,6 +21294,9 @@
       <x:c r="I504" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J504" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="505" ht="24" customHeight="1">
       <x:c r="A505" s="6" t="s">
@@ -20145,6 +21320,9 @@
       <x:c r="I505" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J505" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="506" ht="24" customHeight="1">
       <x:c r="A506" s="6" t="s">
@@ -20168,6 +21346,9 @@
       <x:c r="I506" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J506" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="507" ht="24" customHeight="1">
       <x:c r="A507" s="6" t="s">
@@ -20191,6 +21372,9 @@
       <x:c r="I507" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J507" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="508" ht="24" customHeight="1">
       <x:c r="A508" s="6" t="s">
@@ -20217,6 +21401,9 @@
       <x:c r="I508" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J508" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="509" ht="24" customHeight="1">
       <x:c r="A509" s="6" t="s">
@@ -20243,6 +21430,9 @@
       <x:c r="I509" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J509" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="510" ht="24" customHeight="1">
       <x:c r="A510" s="6" t="s">
@@ -20269,6 +21459,9 @@
       <x:c r="I510" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J510" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="511" ht="24" customHeight="1">
       <x:c r="A511" s="6" t="s">
@@ -20295,6 +21488,9 @@
       <x:c r="I511" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J511" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="512" ht="24" customHeight="1">
       <x:c r="A512" s="6" t="s">
@@ -20318,6 +21514,9 @@
       <x:c r="I512" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J512" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="513" ht="24" customHeight="1">
       <x:c r="A513" s="6" t="s">
@@ -20344,6 +21543,9 @@
       <x:c r="I513" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J513" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="514" ht="24" customHeight="1">
       <x:c r="A514" s="6" t="s">
@@ -20370,6 +21572,9 @@
       <x:c r="I514" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J514" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="515" ht="24" customHeight="1">
       <x:c r="A515" s="6" t="s">
@@ -20396,6 +21601,9 @@
       <x:c r="I515" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J515" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="516" ht="24" customHeight="1">
       <x:c r="A516" s="6" t="s">
@@ -20419,6 +21627,9 @@
       <x:c r="I516" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J516" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="517" ht="24" customHeight="1">
       <x:c r="A517" s="6" t="s">
@@ -20445,6 +21656,9 @@
       <x:c r="I517" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J517" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="518" ht="24" customHeight="1">
       <x:c r="A518" s="6" t="s">
@@ -20471,6 +21685,9 @@
       <x:c r="I518" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J518" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="519" ht="24" customHeight="1">
       <x:c r="A519" s="6" t="s">
@@ -20497,6 +21714,9 @@
       <x:c r="I519" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J519" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="520" ht="24" customHeight="1">
       <x:c r="A520" s="6" t="s">
@@ -20520,6 +21740,9 @@
       <x:c r="I520" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J520" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="521" ht="24" customHeight="1">
       <x:c r="A521" s="6" t="s">
@@ -20546,6 +21769,9 @@
       <x:c r="I521" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J521" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="522" ht="24" customHeight="1">
       <x:c r="A522" s="6" t="s">
@@ -20569,6 +21795,9 @@
       <x:c r="I522" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J522" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="523" ht="24" customHeight="1">
       <x:c r="A523" s="6" t="s">
@@ -20592,6 +21821,9 @@
       <x:c r="I523" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J523" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="524" ht="24" customHeight="1">
       <x:c r="A524" s="6" t="s">
@@ -20615,6 +21847,9 @@
       <x:c r="I524" s="66">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J524" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="525" ht="24" customHeight="1">
       <x:c r="A525" s="9" t="s">
@@ -20641,6 +21876,9 @@
       <x:c r="I525" s="67">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J525" s="178" t="str">
+        <x:v>Discontinued / Request Basis</x:v>
+      </x:c>
     </x:row>
     <x:row r="526">
       <x:c r="A526" t="s">
@@ -20658,6 +21896,9 @@
       <x:c r="I526" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J526" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="527">
       <x:c r="A527" t="s">
@@ -20675,6 +21916,9 @@
       <x:c r="I527" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J527" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="528">
       <x:c r="A528" t="s">
@@ -20692,6 +21936,9 @@
       <x:c r="I528" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J528" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="529" ht="14">
       <x:c r="A529" t="s">
@@ -20718,6 +21965,9 @@
       <x:c r="I529" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J529" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="530" ht="14">
       <x:c r="A530" t="s">
@@ -20744,6 +21994,9 @@
       <x:c r="I530" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J530" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="531" ht="14">
       <x:c r="A531" t="s">
@@ -20770,6 +22023,9 @@
       <x:c r="I531" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J531" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="532">
       <x:c r="A532" t="s">
@@ -20787,6 +22043,9 @@
       <x:c r="I532" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J532" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="533">
       <x:c r="A533" t="s">
@@ -20804,6 +22063,9 @@
       <x:c r="I533" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J533" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="534">
       <x:c r="A534" t="s">
@@ -20821,6 +22083,9 @@
       <x:c r="I534" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J534" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="535">
       <x:c r="A535" t="s">
@@ -20838,6 +22103,9 @@
       <x:c r="I535" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J535" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="536">
       <x:c r="A536" t="s">
@@ -20855,6 +22123,9 @@
       <x:c r="I536" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J536" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="537">
       <x:c r="A537" t="s">
@@ -20872,6 +22143,9 @@
       <x:c r="I537" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J537" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="538">
       <x:c r="A538" t="s">
@@ -20889,6 +22163,9 @@
       <x:c r="I538" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J538" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="539">
       <x:c r="A539" t="s">
@@ -20906,6 +22183,9 @@
       <x:c r="I539" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J539" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="540">
       <x:c r="A540" t="s">
@@ -20923,6 +22203,9 @@
       <x:c r="I540" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J540" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="541" ht="14">
       <x:c r="A541" t="s">
@@ -20949,6 +22232,9 @@
       <x:c r="I541" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J541" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="542">
       <x:c r="A542" t="s">
@@ -20966,6 +22252,9 @@
       <x:c r="I542" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J542" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="543">
       <x:c r="A543" t="s">
@@ -20983,6 +22272,9 @@
       <x:c r="I543" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J543" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="544">
       <x:c r="A544" t="s">
@@ -21000,6 +22292,9 @@
       <x:c r="I544" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J544" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="545">
       <x:c r="A545" t="s">
@@ -21017,6 +22312,9 @@
       <x:c r="I545" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J545" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="546" ht="14">
       <x:c r="A546" t="s">
@@ -21040,6 +22338,9 @@
       <x:c r="I546" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J546" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="547" ht="14">
       <x:c r="A547" t="s">
@@ -21063,6 +22364,9 @@
       <x:c r="I547" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J547" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="548">
       <x:c r="A548" t="s">
@@ -21080,6 +22384,9 @@
       <x:c r="I548" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J548" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="549">
       <x:c r="A549" t="s">
@@ -21097,6 +22404,9 @@
       <x:c r="I549" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J549" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
     <x:row r="550" ht="14">
       <x:c r="A550" t="s">
@@ -21123,11 +22433,22 @@
       <x:c r="I550" s="68">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="J550" s="178" t="str">
+        <x:v>Discontinued</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="J2:J550">
+    <x:cfRule type="expression" dxfId="3" priority="1">
+      <x:formula>$J2="Discontinued"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="4" priority="2">
+      <x:formula>$J2="Discontinued / Request Basis"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R618022d35f454eac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fc9e8ac6fa24df3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28977,7 +30298,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ffd88d446114a5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77e578b80a9492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30099,7 +31420,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b63d2c3d14e44fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0066da726634072"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35414,7 +36735,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9e476144fb547b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d132d5ff50041e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/data/TY_Product_Database.xlsx
+++ b/data/TY_Product_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evanfoo/Documents/Codex/2026-09-07/in/outputs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6815C0-1379-3C4E-BD48-49BEA5E9BB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC3C771-F9B5-594D-ABD5-DCEC57F2D1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33600" yWindow="600" windowWidth="21680" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7519" uniqueCount="2538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7614" uniqueCount="2571">
   <si>
     <t>TY Product Database</t>
   </si>
@@ -8004,6 +8004,106 @@
   </si>
   <si>
     <t>Gelato Display</t>
+  </si>
+  <si>
+    <t>1631(W) x 1003(D) x 1200(H)</t>
+  </si>
+  <si>
+    <t>[360 x 165 x 120H]: 9+9
+360 x 250 x 80H: 6+6</t>
+  </si>
+  <si>
+    <t>-18°C ~ -2°C</t>
+  </si>
+  <si>
+    <t>R452A</t>
+  </si>
+  <si>
+    <t>1 Phase / 230V / 50Hz / 2.0kW / 9A / 20A Isolator</t>
+  </si>
+  <si>
+    <t>sam80.png</t>
+  </si>
+  <si>
+    <t>YDSC-45FT-PC900H</t>
+  </si>
+  <si>
+    <t>1350(W) x 1180(D) x 1200(H) (Including End Panel)</t>
+  </si>
+  <si>
+    <t>238L</t>
+  </si>
+  <si>
+    <t>-1 ̊C ~ +5 ̊C</t>
+  </si>
+  <si>
+    <t>1 Phase / 220~240V / 50Hz / 15A Plug</t>
+  </si>
+  <si>
+    <t>ydsc-45ft-pc900h.png</t>
+  </si>
+  <si>
+    <t>RTSC-6FT-P1245H</t>
+  </si>
+  <si>
+    <t>Service Counter Chiller</t>
+  </si>
+  <si>
+    <t>1935(W) x 1115(D) x 1245(H) mm</t>
+  </si>
+  <si>
+    <t>rtsc-6ft-p1245h.png</t>
+  </si>
+  <si>
+    <t>Carrier</t>
+  </si>
+  <si>
+    <t>Narrow Service Counter</t>
+  </si>
+  <si>
+    <t>1350(W) x 1020(D) x 1165(H)</t>
+  </si>
+  <si>
+    <t>0.16m³</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz / 4.8kwh/24hr / 2.15A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sn-125-72-p-g.png </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN-125-72-P-G </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN-188-72-P-G </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN-250-72-P-G </t>
+  </si>
+  <si>
+    <t>1975(W) x 1020(D) x 1165(H)</t>
+  </si>
+  <si>
+    <t>2600(W) x 1020(D) x 1165(H)</t>
+  </si>
+  <si>
+    <t>0.24m³</t>
+  </si>
+  <si>
+    <t>0.32m³</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz / 6.9kwh/24hr / 3.49A</t>
+  </si>
+  <si>
+    <t>1 Phase / 220V / 50Hz / 10kwh/24hr / 3.86A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sn-188-72-p-g.png </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sn-250-72-p-g.png </t>
   </si>
 </sst>
 </file>
@@ -8624,7 +8724,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpecificationsTable" displayName="SpecificationsTable" ref="A1:R333" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="SpecificationsTable" displayName="SpecificationsTable" ref="A1:R338" totalsRowShown="0">
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Product Type"/>
@@ -25391,7 +25491,7 @@
   <sheetPr>
     <tabColor rgb="FF1686B0"/>
   </sheetPr>
-  <dimension ref="A1:R333"/>
+  <dimension ref="A1:R338"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -30128,7 +30228,9 @@
       <c r="M107" s="46"/>
       <c r="N107" s="46"/>
       <c r="O107" s="47"/>
-      <c r="P107" s="47"/>
+      <c r="P107" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q107" s="48"/>
       <c r="R107" s="49"/>
     </row>
@@ -30160,7 +30262,9 @@
       <c r="M108" s="46"/>
       <c r="N108" s="46"/>
       <c r="O108" s="47"/>
-      <c r="P108" s="47"/>
+      <c r="P108" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q108" s="48"/>
       <c r="R108" s="49"/>
     </row>
@@ -30192,7 +30296,9 @@
       <c r="M109" s="46"/>
       <c r="N109" s="46"/>
       <c r="O109" s="47"/>
-      <c r="P109" s="47"/>
+      <c r="P109" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q109" s="48"/>
       <c r="R109" s="49"/>
     </row>
@@ -30224,7 +30330,9 @@
       <c r="M110" s="46"/>
       <c r="N110" s="46"/>
       <c r="O110" s="47"/>
-      <c r="P110" s="47"/>
+      <c r="P110" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q110" s="48"/>
       <c r="R110" s="49"/>
     </row>
@@ -30256,7 +30364,9 @@
       <c r="M111" s="46"/>
       <c r="N111" s="46"/>
       <c r="O111" s="47"/>
-      <c r="P111" s="47"/>
+      <c r="P111" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q111" s="48"/>
       <c r="R111" s="49"/>
     </row>
@@ -30288,7 +30398,9 @@
       <c r="M112" s="46"/>
       <c r="N112" s="46"/>
       <c r="O112" s="47"/>
-      <c r="P112" s="47"/>
+      <c r="P112" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q112" s="48"/>
       <c r="R112" s="49"/>
     </row>
@@ -30320,7 +30432,9 @@
       <c r="M113" s="46"/>
       <c r="N113" s="46"/>
       <c r="O113" s="47"/>
-      <c r="P113" s="47"/>
+      <c r="P113" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q113" s="48"/>
       <c r="R113" s="49"/>
     </row>
@@ -30352,7 +30466,9 @@
       <c r="M114" s="46"/>
       <c r="N114" s="46"/>
       <c r="O114" s="47"/>
-      <c r="P114" s="47"/>
+      <c r="P114" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q114" s="48"/>
       <c r="R114" s="49"/>
     </row>
@@ -30384,7 +30500,9 @@
       <c r="M115" s="46"/>
       <c r="N115" s="46"/>
       <c r="O115" s="47"/>
-      <c r="P115" s="47"/>
+      <c r="P115" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q115" s="48"/>
       <c r="R115" s="49"/>
     </row>
@@ -30416,7 +30534,9 @@
       <c r="M116" s="46"/>
       <c r="N116" s="46"/>
       <c r="O116" s="47"/>
-      <c r="P116" s="47"/>
+      <c r="P116" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q116" s="48"/>
       <c r="R116" s="49"/>
     </row>
@@ -32128,7 +32248,9 @@
       <c r="M156" s="46"/>
       <c r="N156" s="46"/>
       <c r="O156" s="47"/>
-      <c r="P156" s="47"/>
+      <c r="P156" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q156" s="48"/>
       <c r="R156" s="49"/>
     </row>
@@ -32160,7 +32282,9 @@
       <c r="M157" s="46"/>
       <c r="N157" s="46"/>
       <c r="O157" s="47"/>
-      <c r="P157" s="47"/>
+      <c r="P157" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q157" s="48"/>
       <c r="R157" s="49"/>
     </row>
@@ -32192,7 +32316,9 @@
       <c r="M158" s="46"/>
       <c r="N158" s="46"/>
       <c r="O158" s="47"/>
-      <c r="P158" s="47"/>
+      <c r="P158" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q158" s="48"/>
       <c r="R158" s="49"/>
     </row>
@@ -32224,7 +32350,9 @@
       <c r="M159" s="46"/>
       <c r="N159" s="46"/>
       <c r="O159" s="47"/>
-      <c r="P159" s="47"/>
+      <c r="P159" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q159" s="48"/>
       <c r="R159" s="49"/>
     </row>
@@ -32256,7 +32384,9 @@
       <c r="M160" s="46"/>
       <c r="N160" s="46"/>
       <c r="O160" s="47"/>
-      <c r="P160" s="47"/>
+      <c r="P160" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q160" s="48"/>
       <c r="R160" s="49"/>
     </row>
@@ -32288,7 +32418,9 @@
       <c r="M161" s="46"/>
       <c r="N161" s="46"/>
       <c r="O161" s="47"/>
-      <c r="P161" s="47"/>
+      <c r="P161" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q161" s="48"/>
       <c r="R161" s="49"/>
     </row>
@@ -32320,7 +32452,9 @@
       <c r="M162" s="46"/>
       <c r="N162" s="46"/>
       <c r="O162" s="47"/>
-      <c r="P162" s="47"/>
+      <c r="P162" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q162" s="48"/>
       <c r="R162" s="49"/>
     </row>
@@ -32352,7 +32486,9 @@
       <c r="M163" s="46"/>
       <c r="N163" s="46"/>
       <c r="O163" s="47"/>
-      <c r="P163" s="47"/>
+      <c r="P163" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q163" s="48"/>
       <c r="R163" s="49"/>
     </row>
@@ -32384,7 +32520,9 @@
       <c r="M164" s="46"/>
       <c r="N164" s="46"/>
       <c r="O164" s="47"/>
-      <c r="P164" s="47"/>
+      <c r="P164" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q164" s="48"/>
       <c r="R164" s="49"/>
     </row>
@@ -32416,7 +32554,9 @@
       <c r="M165" s="46"/>
       <c r="N165" s="46"/>
       <c r="O165" s="47"/>
-      <c r="P165" s="47"/>
+      <c r="P165" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q165" s="48"/>
       <c r="R165" s="49"/>
     </row>
@@ -32448,7 +32588,9 @@
       <c r="M166" s="46"/>
       <c r="N166" s="46"/>
       <c r="O166" s="47"/>
-      <c r="P166" s="47"/>
+      <c r="P166" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q166" s="48"/>
       <c r="R166" s="49"/>
     </row>
@@ -32480,7 +32622,9 @@
       <c r="M167" s="46"/>
       <c r="N167" s="46"/>
       <c r="O167" s="47"/>
-      <c r="P167" s="47"/>
+      <c r="P167" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q167" s="48"/>
       <c r="R167" s="49"/>
     </row>
@@ -32512,7 +32656,9 @@
       <c r="M168" s="46"/>
       <c r="N168" s="46"/>
       <c r="O168" s="47"/>
-      <c r="P168" s="47"/>
+      <c r="P168" s="47" t="s">
+        <v>1531</v>
+      </c>
       <c r="Q168" s="48"/>
       <c r="R168" s="49"/>
     </row>
@@ -38868,23 +39014,43 @@
       <c r="E306" s="54" t="s">
         <v>2537</v>
       </c>
-      <c r="F306" s="54"/>
-      <c r="G306" s="55"/>
-      <c r="H306" s="55"/>
-      <c r="I306" s="54"/>
-      <c r="J306" s="54"/>
-      <c r="K306" s="54"/>
-      <c r="L306" s="54"/>
+      <c r="F306" s="54" t="s">
+        <v>2538</v>
+      </c>
+      <c r="G306" s="55" t="s">
+        <v>2539</v>
+      </c>
+      <c r="H306" s="55" t="s">
+        <v>2540</v>
+      </c>
+      <c r="I306" s="54" t="s">
+        <v>2541</v>
+      </c>
+      <c r="J306" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K306" s="54" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L306" s="54" t="s">
+        <v>2542</v>
+      </c>
       <c r="M306" s="56"/>
       <c r="N306" s="56"/>
       <c r="O306" s="47"/>
       <c r="P306" s="47"/>
       <c r="Q306" s="48"/>
-      <c r="R306" s="49"/>
+      <c r="R306" s="49" t="s">
+        <v>2543</v>
+      </c>
     </row>
     <row r="307" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A307" s="53"/>
-      <c r="B307" s="53"/>
+      <c r="A307" s="53" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B307" s="53" t="s">
+        <v>2259</v>
+      </c>
       <c r="C307" s="54"/>
       <c r="D307" s="54"/>
       <c r="E307" s="54"/>
@@ -38903,8 +39069,12 @@
       <c r="R307" s="49"/>
     </row>
     <row r="308" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A308" s="53"/>
-      <c r="B308" s="53"/>
+      <c r="A308" s="53" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B308" s="53" t="s">
+        <v>2260</v>
+      </c>
       <c r="C308" s="54"/>
       <c r="D308" s="54"/>
       <c r="E308" s="54"/>
@@ -38918,9 +39088,7 @@
       <c r="M308" s="56"/>
       <c r="N308" s="56"/>
       <c r="O308" s="47"/>
-      <c r="P308" s="47" t="s">
-        <v>1829</v>
-      </c>
+      <c r="P308" s="47"/>
       <c r="Q308" s="48"/>
       <c r="R308" s="49"/>
     </row>
@@ -38929,7 +39097,7 @@
         <v>2257</v>
       </c>
       <c r="B309" s="53" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="C309" s="54"/>
       <c r="D309" s="54"/>
@@ -38950,10 +39118,10 @@
     </row>
     <row r="310" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="53" t="s">
-        <v>2257</v>
+        <v>2262</v>
       </c>
       <c r="B310" s="53" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="C310" s="54"/>
       <c r="D310" s="54"/>
@@ -38974,10 +39142,10 @@
     </row>
     <row r="311" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="53" t="s">
-        <v>2257</v>
+        <v>2262</v>
       </c>
       <c r="B311" s="53" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="C311" s="54"/>
       <c r="D311" s="54"/>
@@ -39001,7 +39169,7 @@
         <v>2262</v>
       </c>
       <c r="B312" s="53" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="C312" s="54"/>
       <c r="D312" s="54"/>
@@ -39025,7 +39193,7 @@
         <v>2262</v>
       </c>
       <c r="B313" s="53" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="C313" s="54"/>
       <c r="D313" s="54"/>
@@ -39049,7 +39217,7 @@
         <v>2262</v>
       </c>
       <c r="B314" s="53" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="C314" s="54"/>
       <c r="D314" s="54"/>
@@ -39070,10 +39238,10 @@
     </row>
     <row r="315" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="53" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="B315" s="53" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="C315" s="54"/>
       <c r="D315" s="54"/>
@@ -39094,10 +39262,10 @@
     </row>
     <row r="316" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="53" t="s">
-        <v>2262</v>
+        <v>2269</v>
       </c>
       <c r="B316" s="53" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="C316" s="54"/>
       <c r="D316" s="54"/>
@@ -39118,131 +39286,237 @@
     </row>
     <row r="317" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="53" t="s">
-        <v>2257</v>
+        <v>1521</v>
       </c>
       <c r="B317" s="53" t="s">
-        <v>2268</v>
-      </c>
-      <c r="C317" s="54"/>
-      <c r="D317" s="54"/>
-      <c r="E317" s="54"/>
-      <c r="F317" s="54"/>
-      <c r="G317" s="55"/>
-      <c r="H317" s="55"/>
-      <c r="I317" s="54"/>
-      <c r="J317" s="54"/>
-      <c r="K317" s="54"/>
-      <c r="L317" s="54"/>
+        <v>1689</v>
+      </c>
+      <c r="C317" s="54" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D317" s="54" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E317" s="54" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F317" s="54" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G317" s="55" t="s">
+        <v>2546</v>
+      </c>
+      <c r="H317" s="55" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I317" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="J317" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K317" s="54" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L317" s="54" t="s">
+        <v>2548</v>
+      </c>
       <c r="M317" s="56"/>
       <c r="N317" s="56"/>
       <c r="O317" s="47"/>
       <c r="P317" s="47"/>
       <c r="Q317" s="48"/>
-      <c r="R317" s="49"/>
+      <c r="R317" s="49" t="s">
+        <v>2549</v>
+      </c>
     </row>
     <row r="318" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="53" t="s">
-        <v>2269</v>
+        <v>1521</v>
       </c>
       <c r="B318" s="53" t="s">
-        <v>2270</v>
-      </c>
-      <c r="C318" s="54"/>
-      <c r="D318" s="54"/>
-      <c r="E318" s="54"/>
-      <c r="F318" s="54"/>
-      <c r="G318" s="55"/>
-      <c r="H318" s="55"/>
-      <c r="I318" s="54"/>
-      <c r="J318" s="54"/>
-      <c r="K318" s="54"/>
-      <c r="L318" s="54"/>
+        <v>1689</v>
+      </c>
+      <c r="C318" s="54" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D318" s="54" t="s">
+        <v>2550</v>
+      </c>
+      <c r="E318" s="54" t="s">
+        <v>2551</v>
+      </c>
+      <c r="F318" s="54" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G318" s="55" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H318" s="55" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I318" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="J318" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K318" s="54" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L318" s="54" t="s">
+        <v>2548</v>
+      </c>
       <c r="M318" s="56"/>
       <c r="N318" s="56"/>
       <c r="O318" s="47"/>
       <c r="P318" s="47"/>
       <c r="Q318" s="48"/>
-      <c r="R318" s="49"/>
+      <c r="R318" s="49" t="s">
+        <v>2553</v>
+      </c>
     </row>
     <row r="319" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="53" t="s">
-        <v>2271</v>
+        <v>1521</v>
       </c>
       <c r="B319" s="53" t="s">
-        <v>2272</v>
-      </c>
-      <c r="C319" s="54"/>
-      <c r="D319" s="54"/>
-      <c r="E319" s="54"/>
-      <c r="F319" s="54"/>
-      <c r="G319" s="55"/>
-      <c r="H319" s="55"/>
-      <c r="I319" s="54"/>
-      <c r="J319" s="54"/>
-      <c r="K319" s="54"/>
-      <c r="L319" s="54"/>
+        <v>1689</v>
+      </c>
+      <c r="C319" s="54" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D319" s="54" t="s">
+        <v>2560</v>
+      </c>
+      <c r="E319" s="54" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F319" s="54" t="s">
+        <v>2556</v>
+      </c>
+      <c r="G319" s="55" t="s">
+        <v>2557</v>
+      </c>
+      <c r="H319" s="55" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I319" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="J319" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K319" s="54" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L319" s="54" t="s">
+        <v>2558</v>
+      </c>
       <c r="M319" s="56"/>
       <c r="N319" s="56"/>
       <c r="O319" s="47"/>
       <c r="P319" s="47"/>
       <c r="Q319" s="48"/>
-      <c r="R319" s="49"/>
+      <c r="R319" s="49" t="s">
+        <v>2559</v>
+      </c>
     </row>
     <row r="320" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="53" t="s">
-        <v>2271</v>
+        <v>1521</v>
       </c>
       <c r="B320" s="53" t="s">
-        <v>2273</v>
-      </c>
-      <c r="C320" s="54"/>
-      <c r="D320" s="54"/>
-      <c r="E320" s="54"/>
-      <c r="F320" s="54"/>
-      <c r="G320" s="55"/>
-      <c r="H320" s="55"/>
-      <c r="I320" s="54"/>
-      <c r="J320" s="54"/>
-      <c r="K320" s="54"/>
-      <c r="L320" s="54"/>
+        <v>1689</v>
+      </c>
+      <c r="C320" s="54" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D320" s="54" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E320" s="54" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F320" s="54" t="s">
+        <v>2563</v>
+      </c>
+      <c r="G320" s="55" t="s">
+        <v>2565</v>
+      </c>
+      <c r="H320" s="55" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I320" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="J320" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K320" s="54" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L320" s="54" t="s">
+        <v>2567</v>
+      </c>
       <c r="M320" s="56"/>
       <c r="N320" s="56"/>
       <c r="O320" s="47"/>
       <c r="P320" s="47"/>
       <c r="Q320" s="48"/>
-      <c r="R320" s="49"/>
+      <c r="R320" s="49" t="s">
+        <v>2569</v>
+      </c>
     </row>
     <row r="321" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="53" t="s">
-        <v>2271</v>
+        <v>1521</v>
       </c>
       <c r="B321" s="53" t="s">
-        <v>2274</v>
-      </c>
-      <c r="C321" s="54"/>
-      <c r="D321" s="54"/>
-      <c r="E321" s="54"/>
-      <c r="F321" s="54"/>
-      <c r="G321" s="55"/>
-      <c r="H321" s="55"/>
-      <c r="I321" s="54"/>
-      <c r="J321" s="54"/>
-      <c r="K321" s="54"/>
-      <c r="L321" s="54"/>
+        <v>1689</v>
+      </c>
+      <c r="C321" s="54" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D321" s="54" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E321" s="54" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F321" s="54" t="s">
+        <v>2564</v>
+      </c>
+      <c r="G321" s="55" t="s">
+        <v>2566</v>
+      </c>
+      <c r="H321" s="55" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I321" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="J321" s="44" t="s">
+        <v>1984</v>
+      </c>
+      <c r="K321" s="54" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L321" s="54" t="s">
+        <v>2568</v>
+      </c>
       <c r="M321" s="56"/>
       <c r="N321" s="56"/>
       <c r="O321" s="47"/>
       <c r="P321" s="47"/>
       <c r="Q321" s="48"/>
-      <c r="R321" s="49"/>
+      <c r="R321" s="49" t="s">
+        <v>2570</v>
+      </c>
     </row>
     <row r="322" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A322" s="53" t="s">
-        <v>2271</v>
-      </c>
-      <c r="B322" s="53" t="s">
-        <v>2275</v>
-      </c>
+      <c r="A322" s="53"/>
+      <c r="B322" s="53"/>
       <c r="C322" s="54"/>
       <c r="D322" s="54"/>
       <c r="E322" s="54"/>
@@ -39261,12 +39535,8 @@
       <c r="R322" s="49"/>
     </row>
     <row r="323" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A323" s="53" t="s">
-        <v>2276</v>
-      </c>
-      <c r="B323" s="53" t="s">
-        <v>2277</v>
-      </c>
+      <c r="A323" s="53"/>
+      <c r="B323" s="53"/>
       <c r="C323" s="54"/>
       <c r="D323" s="54"/>
       <c r="E323" s="54"/>
@@ -39286,10 +39556,10 @@
     </row>
     <row r="324" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="53" t="s">
-        <v>2276</v>
+        <v>2271</v>
       </c>
       <c r="B324" s="53" t="s">
-        <v>2278</v>
+        <v>2272</v>
       </c>
       <c r="C324" s="54"/>
       <c r="D324" s="54"/>
@@ -39310,10 +39580,10 @@
     </row>
     <row r="325" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="53" t="s">
-        <v>2276</v>
+        <v>2271</v>
       </c>
       <c r="B325" s="53" t="s">
-        <v>2279</v>
+        <v>2273</v>
       </c>
       <c r="C325" s="54"/>
       <c r="D325" s="54"/>
@@ -39334,10 +39604,10 @@
     </row>
     <row r="326" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="53" t="s">
-        <v>2280</v>
+        <v>2271</v>
       </c>
       <c r="B326" s="53" t="s">
-        <v>2281</v>
+        <v>2274</v>
       </c>
       <c r="C326" s="54"/>
       <c r="D326" s="54"/>
@@ -39358,10 +39628,10 @@
     </row>
     <row r="327" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="53" t="s">
-        <v>2280</v>
+        <v>2271</v>
       </c>
       <c r="B327" s="53" t="s">
-        <v>2282</v>
+        <v>2275</v>
       </c>
       <c r="C327" s="54"/>
       <c r="D327" s="54"/>
@@ -39382,10 +39652,10 @@
     </row>
     <row r="328" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="53" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
       <c r="B328" s="53" t="s">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="C328" s="54"/>
       <c r="D328" s="54"/>
@@ -39406,10 +39676,10 @@
     </row>
     <row r="329" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="53" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
       <c r="B329" s="53" t="s">
-        <v>2284</v>
+        <v>2278</v>
       </c>
       <c r="C329" s="54"/>
       <c r="D329" s="54"/>
@@ -39430,10 +39700,10 @@
     </row>
     <row r="330" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="53" t="s">
-        <v>2280</v>
+        <v>2276</v>
       </c>
       <c r="B330" s="53" t="s">
-        <v>2285</v>
+        <v>2279</v>
       </c>
       <c r="C330" s="54"/>
       <c r="D330" s="54"/>
@@ -39457,7 +39727,7 @@
         <v>2280</v>
       </c>
       <c r="B331" s="53" t="s">
-        <v>2286</v>
+        <v>2281</v>
       </c>
       <c r="C331" s="54"/>
       <c r="D331" s="54"/>
@@ -39481,7 +39751,7 @@
         <v>2280</v>
       </c>
       <c r="B332" s="53" t="s">
-        <v>2287</v>
+        <v>2282</v>
       </c>
       <c r="C332" s="54"/>
       <c r="D332" s="54"/>
@@ -39505,7 +39775,7 @@
         <v>2280</v>
       </c>
       <c r="B333" s="53" t="s">
-        <v>2288</v>
+        <v>2283</v>
       </c>
       <c r="C333" s="54"/>
       <c r="D333" s="54"/>
@@ -39524,25 +39794,145 @@
       <c r="Q333" s="48"/>
       <c r="R333" s="49"/>
     </row>
+    <row r="334" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A334" s="53" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B334" s="53" t="s">
+        <v>2284</v>
+      </c>
+      <c r="C334" s="54"/>
+      <c r="D334" s="54"/>
+      <c r="E334" s="54"/>
+      <c r="F334" s="54"/>
+      <c r="G334" s="55"/>
+      <c r="H334" s="55"/>
+      <c r="I334" s="54"/>
+      <c r="J334" s="54"/>
+      <c r="K334" s="54"/>
+      <c r="L334" s="54"/>
+      <c r="M334" s="56"/>
+      <c r="N334" s="56"/>
+      <c r="O334" s="47"/>
+      <c r="P334" s="47"/>
+      <c r="Q334" s="48"/>
+      <c r="R334" s="49"/>
+    </row>
+    <row r="335" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A335" s="53" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B335" s="53" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C335" s="54"/>
+      <c r="D335" s="54"/>
+      <c r="E335" s="54"/>
+      <c r="F335" s="54"/>
+      <c r="G335" s="55"/>
+      <c r="H335" s="55"/>
+      <c r="I335" s="54"/>
+      <c r="J335" s="54"/>
+      <c r="K335" s="54"/>
+      <c r="L335" s="54"/>
+      <c r="M335" s="56"/>
+      <c r="N335" s="56"/>
+      <c r="O335" s="47"/>
+      <c r="P335" s="47"/>
+      <c r="Q335" s="48"/>
+      <c r="R335" s="49"/>
+    </row>
+    <row r="336" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A336" s="53" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B336" s="53" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C336" s="54"/>
+      <c r="D336" s="54"/>
+      <c r="E336" s="54"/>
+      <c r="F336" s="54"/>
+      <c r="G336" s="55"/>
+      <c r="H336" s="55"/>
+      <c r="I336" s="54"/>
+      <c r="J336" s="54"/>
+      <c r="K336" s="54"/>
+      <c r="L336" s="54"/>
+      <c r="M336" s="56"/>
+      <c r="N336" s="56"/>
+      <c r="O336" s="47"/>
+      <c r="P336" s="47"/>
+      <c r="Q336" s="48"/>
+      <c r="R336" s="49"/>
+    </row>
+    <row r="337" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A337" s="53" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B337" s="53" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C337" s="54"/>
+      <c r="D337" s="54"/>
+      <c r="E337" s="54"/>
+      <c r="F337" s="54"/>
+      <c r="G337" s="55"/>
+      <c r="H337" s="55"/>
+      <c r="I337" s="54"/>
+      <c r="J337" s="54"/>
+      <c r="K337" s="54"/>
+      <c r="L337" s="54"/>
+      <c r="M337" s="56"/>
+      <c r="N337" s="56"/>
+      <c r="O337" s="47"/>
+      <c r="P337" s="47"/>
+      <c r="Q337" s="48"/>
+      <c r="R337" s="49"/>
+    </row>
+    <row r="338" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A338" s="53" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B338" s="53" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C338" s="54"/>
+      <c r="D338" s="54"/>
+      <c r="E338" s="54"/>
+      <c r="F338" s="54"/>
+      <c r="G338" s="55"/>
+      <c r="H338" s="55"/>
+      <c r="I338" s="54"/>
+      <c r="J338" s="54"/>
+      <c r="K338" s="54"/>
+      <c r="L338" s="54"/>
+      <c r="M338" s="56"/>
+      <c r="N338" s="56"/>
+      <c r="O338" s="47"/>
+      <c r="P338" s="47"/>
+      <c r="Q338" s="48"/>
+      <c r="R338" s="49"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
     <dataValidation type="list" sqref="I177:I191 I122:I132 I145:I146 I30:I119 L31:L119" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Yes,No,Pending,Not applicable"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="A2:A433" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="A2:A438" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Refrigeration,Ice,Displays,Warewashing,Frozen dessert,Cooking,Supermarket Display,Sushi,Cold Room,Cooking Range"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="B2:B433" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" sqref="B2:B438" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Upright refrigerators,Undercounter refrigerators,Blast freezers,Ice makers,Chest freezers,Cake and pastry displays,Flower displays,Glass-door displays,Undercounter displays,Tabletop displays,Dishwashers,Ice-cream and gelato displays,Gelato storage freezer"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K433" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="list" sqref="K2:K438" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"Yes,No,-"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="P2:P433" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="list" sqref="P2:P438" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
